--- a/_meta/snapshots/oam-75-40-01-fo.xlsx
+++ b/_meta/snapshots/oam-75-40-01-fo.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="U:\OAM Policies\OAM Current\OAM Forms-Ch75 &amp; Misc\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\Wpdasclr05c\cfo\SARS\OAM Policies\OAM Ready to Review\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F56080C2-DFFC-442C-842E-FC575E7E6AFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FD73D6E-E0F4-4591-8576-0AADE60474D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="1170" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10980" yWindow="1350" windowWidth="17865" windowHeight="13665" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2026 TEDS" sheetId="3" r:id="rId1"/>
@@ -41,6 +41,7 @@
     <author>rstuder</author>
     <author>State of Oregon DAS</author>
     <author>VAJRATKAR Shrikant * CFO</author>
+    <author>WILLIAMS Karen A * DAS</author>
   </authors>
   <commentList>
     <comment ref="A5" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
@@ -409,7 +410,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q30" authorId="3" shapeId="0" xr:uid="{6DA94CA6-AA64-4BA0-A461-A666200DC11A}">
+    <comment ref="Q30" authorId="4" shapeId="0" xr:uid="{27BF9834-BCE5-42D7-8C8F-773E1D701773}">
       <text>
         <r>
           <rPr>
@@ -418,11 +419,11 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>Rate effective from January 1, 2026 to date.</t>
+          <t>Rate effective from July 1, 2026 to date.</t>
         </r>
       </text>
     </comment>
-    <comment ref="Q31" authorId="3" shapeId="0" xr:uid="{21AF4272-A498-4944-B893-3B60D1F2DF99}">
+    <comment ref="Q31" authorId="4" shapeId="0" xr:uid="{C29614A1-5F4C-4477-BD77-C290170C8606}">
       <text>
         <r>
           <rPr>
@@ -431,12 +432,39 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Rate effective from January 1, 2026 to date.
+          <t xml:space="preserve">Rate effective from July 1, 2026 to date.
 </t>
         </r>
       </text>
     </comment>
-    <comment ref="Q32" authorId="3" shapeId="0" xr:uid="{00000000-0006-0000-0000-00001A000000}">
+    <comment ref="Q32" authorId="3" shapeId="0" xr:uid="{6DA94CA6-AA64-4BA0-A461-A666200DC11A}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Rate effective from January 1, 2026 to June 30, 2026.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="Q33" authorId="3" shapeId="0" xr:uid="{21AF4272-A498-4944-B893-3B60D1F2DF99}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Rate effective from January 1, 2026 to June 30, 2026.
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="Q34" authorId="3" shapeId="0" xr:uid="{00000000-0006-0000-0000-00001A000000}">
       <text>
         <r>
           <rPr>
@@ -449,7 +477,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q33" authorId="3" shapeId="0" xr:uid="{7B0FD40A-14B3-4171-AC90-DA2BD437B823}">
+    <comment ref="Q35" authorId="3" shapeId="0" xr:uid="{7B0FD40A-14B3-4171-AC90-DA2BD437B823}">
       <text>
         <r>
           <rPr>
@@ -1279,25 +1307,6 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>Rate per Mile</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>: The top 2 rows show the current year rates. Below those are the rates applicable for travel which took place in the prior year.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
       <t>Amount</t>
     </r>
     <r>
@@ -1481,6 +1490,25 @@
         <family val="2"/>
       </rPr>
       <t>: Regular, round-trip distance from residence to central workstation or residence to non-residential alternate workstation (agency to determine). Enter deduction for commute miles, as applicable.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Rate per Mile</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>: The top 2 rows show the current year rates. Below those are the rates applicable for travel which took place either at different rates or in the prior year.</t>
     </r>
   </si>
 </sst>
@@ -1907,7 +1935,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="257">
+  <cellXfs count="258">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2196,91 +2224,529 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="169" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="43" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="43" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="43" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="8" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="8" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="8" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="8" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="9" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="9" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="9" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="18" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="18" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="18" fontId="5" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="18" fontId="5" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="43" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="169" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="5" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="167" fontId="5" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
@@ -2299,479 +2765,41 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="18" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="18" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="18" fontId="5" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="18" fontId="5" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="43" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="9" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="9" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="9" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="44" fontId="8" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="8" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="8" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="8" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -2784,6 +2812,10 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="170" fontId="5" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -3262,188 +3294,188 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="142" t="s">
+      <c r="A1" s="208" t="s">
         <v>51</v>
       </c>
-      <c r="B1" s="142"/>
-      <c r="C1" s="142"/>
-      <c r="D1" s="142"/>
-      <c r="E1" s="142"/>
-      <c r="F1" s="142"/>
-      <c r="G1" s="142"/>
-      <c r="H1" s="140"/>
-      <c r="I1" s="141"/>
-      <c r="J1" s="141"/>
-      <c r="K1" s="141"/>
-      <c r="L1" s="141"/>
-      <c r="M1" s="141"/>
-      <c r="N1" s="141"/>
-      <c r="O1" s="141"/>
-      <c r="P1" s="141"/>
-      <c r="Q1" s="141"/>
-      <c r="R1" s="141"/>
-      <c r="S1" s="141"/>
+      <c r="B1" s="208"/>
+      <c r="C1" s="208"/>
+      <c r="D1" s="208"/>
+      <c r="E1" s="208"/>
+      <c r="F1" s="208"/>
+      <c r="G1" s="208"/>
+      <c r="H1" s="198"/>
+      <c r="I1" s="207"/>
+      <c r="J1" s="207"/>
+      <c r="K1" s="207"/>
+      <c r="L1" s="207"/>
+      <c r="M1" s="207"/>
+      <c r="N1" s="207"/>
+      <c r="O1" s="207"/>
+      <c r="P1" s="207"/>
+      <c r="Q1" s="207"/>
+      <c r="R1" s="207"/>
+      <c r="S1" s="207"/>
       <c r="U1" s="68"/>
     </row>
     <row r="2" spans="1:21" s="7" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="132" t="s">
+      <c r="A2" s="200" t="s">
         <v>25</v>
       </c>
-      <c r="B2" s="132"/>
-      <c r="C2" s="132"/>
-      <c r="D2" s="132"/>
-      <c r="E2" s="132"/>
-      <c r="F2" s="132"/>
-      <c r="G2" s="132"/>
-      <c r="H2" s="141"/>
-      <c r="I2" s="141"/>
-      <c r="J2" s="141"/>
-      <c r="K2" s="141"/>
-      <c r="L2" s="141"/>
-      <c r="M2" s="141"/>
-      <c r="N2" s="141"/>
-      <c r="O2" s="141"/>
-      <c r="P2" s="141"/>
-      <c r="Q2" s="141"/>
-      <c r="R2" s="141"/>
-      <c r="S2" s="141"/>
+      <c r="B2" s="200"/>
+      <c r="C2" s="200"/>
+      <c r="D2" s="200"/>
+      <c r="E2" s="200"/>
+      <c r="F2" s="200"/>
+      <c r="G2" s="200"/>
+      <c r="H2" s="207"/>
+      <c r="I2" s="207"/>
+      <c r="J2" s="207"/>
+      <c r="K2" s="207"/>
+      <c r="L2" s="207"/>
+      <c r="M2" s="207"/>
+      <c r="N2" s="207"/>
+      <c r="O2" s="207"/>
+      <c r="P2" s="207"/>
+      <c r="Q2" s="207"/>
+      <c r="R2" s="207"/>
+      <c r="S2" s="207"/>
     </row>
     <row r="3" spans="1:21" s="7" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="132" t="s">
+      <c r="A3" s="200" t="s">
         <v>52</v>
       </c>
-      <c r="B3" s="132"/>
-      <c r="C3" s="132"/>
-      <c r="D3" s="132"/>
-      <c r="E3" s="132"/>
-      <c r="F3" s="132"/>
-      <c r="G3" s="132"/>
-      <c r="H3" s="141"/>
-      <c r="I3" s="141"/>
-      <c r="J3" s="141"/>
-      <c r="K3" s="141"/>
-      <c r="L3" s="141"/>
-      <c r="M3" s="141"/>
-      <c r="N3" s="141"/>
-      <c r="O3" s="141"/>
-      <c r="P3" s="141"/>
-      <c r="Q3" s="141"/>
-      <c r="R3" s="141"/>
-      <c r="S3" s="141"/>
+      <c r="B3" s="200"/>
+      <c r="C3" s="200"/>
+      <c r="D3" s="200"/>
+      <c r="E3" s="200"/>
+      <c r="F3" s="200"/>
+      <c r="G3" s="200"/>
+      <c r="H3" s="207"/>
+      <c r="I3" s="207"/>
+      <c r="J3" s="207"/>
+      <c r="K3" s="207"/>
+      <c r="L3" s="207"/>
+      <c r="M3" s="207"/>
+      <c r="N3" s="207"/>
+      <c r="O3" s="207"/>
+      <c r="P3" s="207"/>
+      <c r="Q3" s="207"/>
+      <c r="R3" s="207"/>
+      <c r="S3" s="207"/>
     </row>
     <row r="4" spans="1:21" s="7" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="139"/>
-      <c r="B4" s="139"/>
-      <c r="C4" s="139"/>
-      <c r="D4" s="139"/>
-      <c r="E4" s="139"/>
-      <c r="F4" s="139"/>
-      <c r="G4" s="139"/>
-      <c r="H4" s="139"/>
-      <c r="I4" s="139"/>
-      <c r="J4" s="139"/>
-      <c r="K4" s="139"/>
-      <c r="L4" s="139"/>
-      <c r="M4" s="139"/>
-      <c r="N4" s="139"/>
-      <c r="O4" s="139"/>
-      <c r="P4" s="139"/>
-      <c r="Q4" s="139"/>
-      <c r="R4" s="139"/>
-      <c r="S4" s="139"/>
+      <c r="A4" s="206"/>
+      <c r="B4" s="206"/>
+      <c r="C4" s="206"/>
+      <c r="D4" s="206"/>
+      <c r="E4" s="206"/>
+      <c r="F4" s="206"/>
+      <c r="G4" s="206"/>
+      <c r="H4" s="206"/>
+      <c r="I4" s="206"/>
+      <c r="J4" s="206"/>
+      <c r="K4" s="206"/>
+      <c r="L4" s="206"/>
+      <c r="M4" s="206"/>
+      <c r="N4" s="206"/>
+      <c r="O4" s="206"/>
+      <c r="P4" s="206"/>
+      <c r="Q4" s="206"/>
+      <c r="R4" s="206"/>
+      <c r="S4" s="206"/>
     </row>
     <row r="5" spans="1:21" s="8" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="136" t="s">
+      <c r="A5" s="204" t="s">
         <v>0</v>
       </c>
-      <c r="B5" s="137"/>
-      <c r="C5" s="137"/>
-      <c r="D5" s="137"/>
-      <c r="E5" s="137"/>
-      <c r="F5" s="138"/>
-      <c r="G5" s="133" t="s">
+      <c r="B5" s="192"/>
+      <c r="C5" s="192"/>
+      <c r="D5" s="192"/>
+      <c r="E5" s="192"/>
+      <c r="F5" s="205"/>
+      <c r="G5" s="201" t="s">
         <v>1</v>
       </c>
-      <c r="H5" s="134"/>
-      <c r="I5" s="134"/>
-      <c r="J5" s="134"/>
-      <c r="K5" s="135"/>
-      <c r="L5" s="133" t="s">
+      <c r="H5" s="202"/>
+      <c r="I5" s="202"/>
+      <c r="J5" s="202"/>
+      <c r="K5" s="203"/>
+      <c r="L5" s="201" t="s">
         <v>2</v>
       </c>
-      <c r="M5" s="134"/>
-      <c r="N5" s="134"/>
-      <c r="O5" s="134"/>
-      <c r="P5" s="134"/>
-      <c r="Q5" s="134"/>
-      <c r="R5" s="134"/>
-      <c r="S5" s="135"/>
+      <c r="M5" s="202"/>
+      <c r="N5" s="202"/>
+      <c r="O5" s="202"/>
+      <c r="P5" s="202"/>
+      <c r="Q5" s="202"/>
+      <c r="R5" s="202"/>
+      <c r="S5" s="203"/>
     </row>
     <row r="6" spans="1:21" s="9" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="148"/>
-      <c r="B6" s="149"/>
-      <c r="C6" s="149"/>
-      <c r="D6" s="149"/>
-      <c r="E6" s="149"/>
-      <c r="F6" s="150"/>
-      <c r="G6" s="148"/>
-      <c r="H6" s="149"/>
-      <c r="I6" s="149"/>
-      <c r="J6" s="149"/>
-      <c r="K6" s="150"/>
-      <c r="L6" s="156"/>
-      <c r="M6" s="157"/>
-      <c r="N6" s="157"/>
-      <c r="O6" s="157"/>
-      <c r="P6" s="157"/>
-      <c r="Q6" s="157"/>
-      <c r="R6" s="157"/>
-      <c r="S6" s="158"/>
+      <c r="A6" s="213"/>
+      <c r="B6" s="214"/>
+      <c r="C6" s="214"/>
+      <c r="D6" s="214"/>
+      <c r="E6" s="214"/>
+      <c r="F6" s="215"/>
+      <c r="G6" s="213"/>
+      <c r="H6" s="214"/>
+      <c r="I6" s="214"/>
+      <c r="J6" s="214"/>
+      <c r="K6" s="215"/>
+      <c r="L6" s="219"/>
+      <c r="M6" s="220"/>
+      <c r="N6" s="220"/>
+      <c r="O6" s="220"/>
+      <c r="P6" s="220"/>
+      <c r="Q6" s="220"/>
+      <c r="R6" s="220"/>
+      <c r="S6" s="221"/>
     </row>
     <row r="7" spans="1:21" s="10" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="136" t="s">
+      <c r="A7" s="204" t="s">
         <v>3</v>
       </c>
-      <c r="B7" s="137"/>
-      <c r="C7" s="137"/>
-      <c r="D7" s="137"/>
-      <c r="E7" s="137"/>
-      <c r="F7" s="138"/>
-      <c r="G7" s="133" t="s">
+      <c r="B7" s="192"/>
+      <c r="C7" s="192"/>
+      <c r="D7" s="192"/>
+      <c r="E7" s="192"/>
+      <c r="F7" s="205"/>
+      <c r="G7" s="201" t="s">
         <v>53</v>
       </c>
-      <c r="H7" s="134"/>
-      <c r="I7" s="134"/>
-      <c r="J7" s="134"/>
-      <c r="K7" s="135"/>
-      <c r="L7" s="133" t="s">
+      <c r="H7" s="202"/>
+      <c r="I7" s="202"/>
+      <c r="J7" s="202"/>
+      <c r="K7" s="203"/>
+      <c r="L7" s="201" t="s">
         <v>28</v>
       </c>
-      <c r="M7" s="134"/>
-      <c r="N7" s="134"/>
-      <c r="O7" s="134"/>
-      <c r="P7" s="134"/>
-      <c r="Q7" s="134"/>
-      <c r="R7" s="134"/>
-      <c r="S7" s="135"/>
+      <c r="M7" s="202"/>
+      <c r="N7" s="202"/>
+      <c r="O7" s="202"/>
+      <c r="P7" s="202"/>
+      <c r="Q7" s="202"/>
+      <c r="R7" s="202"/>
+      <c r="S7" s="203"/>
     </row>
     <row r="8" spans="1:21" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="153"/>
-      <c r="B8" s="154"/>
-      <c r="C8" s="154"/>
-      <c r="D8" s="154"/>
-      <c r="E8" s="154"/>
-      <c r="F8" s="155"/>
-      <c r="G8" s="148"/>
-      <c r="H8" s="149"/>
-      <c r="I8" s="149"/>
-      <c r="J8" s="149"/>
-      <c r="K8" s="150"/>
+      <c r="A8" s="216"/>
+      <c r="B8" s="217"/>
+      <c r="C8" s="217"/>
+      <c r="D8" s="217"/>
+      <c r="E8" s="217"/>
+      <c r="F8" s="218"/>
+      <c r="G8" s="213"/>
+      <c r="H8" s="214"/>
+      <c r="I8" s="214"/>
+      <c r="J8" s="214"/>
+      <c r="K8" s="215"/>
       <c r="L8" s="11"/>
-      <c r="M8" s="144" t="s">
+      <c r="M8" s="209" t="s">
         <v>23</v>
       </c>
-      <c r="N8" s="144"/>
+      <c r="N8" s="209"/>
       <c r="O8" s="12"/>
       <c r="P8" s="13" t="s">
         <v>9</v>
@@ -3455,80 +3487,80 @@
       <c r="S8" s="77"/>
     </row>
     <row r="9" spans="1:21" s="20" customFormat="1" ht="11.25" x14ac:dyDescent="0.2">
-      <c r="A9" s="176" t="s">
+      <c r="A9" s="186" t="s">
         <v>29</v>
       </c>
-      <c r="B9" s="177"/>
+      <c r="B9" s="187"/>
       <c r="C9" s="16"/>
-      <c r="D9" s="151" t="s">
+      <c r="D9" s="173" t="s">
         <v>4</v>
       </c>
-      <c r="E9" s="151"/>
+      <c r="E9" s="173"/>
       <c r="F9" s="17"/>
       <c r="G9" s="18" t="s">
         <v>5</v>
       </c>
       <c r="H9" s="19"/>
-      <c r="I9" s="152" t="s">
+      <c r="I9" s="166" t="s">
         <v>6</v>
       </c>
-      <c r="J9" s="152"/>
-      <c r="K9" s="152"/>
+      <c r="J9" s="166"/>
+      <c r="K9" s="166"/>
       <c r="L9" s="16"/>
-      <c r="M9" s="152" t="s">
+      <c r="M9" s="166" t="s">
         <v>7</v>
       </c>
-      <c r="N9" s="152"/>
+      <c r="N9" s="166"/>
       <c r="O9" s="17"/>
-      <c r="P9" s="151"/>
-      <c r="Q9" s="151"/>
-      <c r="R9" s="151"/>
-      <c r="S9" s="166"/>
+      <c r="P9" s="173"/>
+      <c r="Q9" s="173"/>
+      <c r="R9" s="173"/>
+      <c r="S9" s="174"/>
     </row>
     <row r="10" spans="1:21" s="20" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="159"/>
-      <c r="B10" s="160"/>
-      <c r="C10" s="160"/>
-      <c r="D10" s="160"/>
-      <c r="E10" s="160"/>
-      <c r="F10" s="160"/>
-      <c r="G10" s="160"/>
-      <c r="H10" s="160"/>
-      <c r="I10" s="160"/>
-      <c r="J10" s="160"/>
-      <c r="K10" s="160"/>
-      <c r="L10" s="160"/>
-      <c r="M10" s="160"/>
-      <c r="N10" s="160"/>
-      <c r="O10" s="160"/>
-      <c r="P10" s="160"/>
-      <c r="Q10" s="160"/>
-      <c r="R10" s="160"/>
-      <c r="S10" s="161"/>
+      <c r="A10" s="167"/>
+      <c r="B10" s="168"/>
+      <c r="C10" s="168"/>
+      <c r="D10" s="168"/>
+      <c r="E10" s="168"/>
+      <c r="F10" s="168"/>
+      <c r="G10" s="168"/>
+      <c r="H10" s="168"/>
+      <c r="I10" s="168"/>
+      <c r="J10" s="168"/>
+      <c r="K10" s="168"/>
+      <c r="L10" s="168"/>
+      <c r="M10" s="168"/>
+      <c r="N10" s="168"/>
+      <c r="O10" s="168"/>
+      <c r="P10" s="168"/>
+      <c r="Q10" s="168"/>
+      <c r="R10" s="168"/>
+      <c r="S10" s="169"/>
     </row>
     <row r="11" spans="1:21" s="10" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="178" t="s">
+      <c r="A11" s="188" t="s">
         <v>8</v>
       </c>
-      <c r="B11" s="179"/>
+      <c r="B11" s="189"/>
       <c r="C11" s="21"/>
-      <c r="D11" s="180"/>
-      <c r="E11" s="170"/>
-      <c r="F11" s="170"/>
-      <c r="G11" s="170"/>
-      <c r="H11" s="170"/>
+      <c r="D11" s="190"/>
+      <c r="E11" s="180"/>
+      <c r="F11" s="180"/>
+      <c r="G11" s="180"/>
+      <c r="H11" s="180"/>
       <c r="I11" s="59" t="s">
         <v>9</v>
       </c>
       <c r="J11" s="22"/>
-      <c r="K11" s="170"/>
-      <c r="L11" s="170"/>
-      <c r="M11" s="170"/>
-      <c r="N11" s="170"/>
-      <c r="O11" s="170"/>
-      <c r="P11" s="170"/>
-      <c r="Q11" s="170"/>
-      <c r="R11" s="170"/>
+      <c r="K11" s="180"/>
+      <c r="L11" s="180"/>
+      <c r="M11" s="180"/>
+      <c r="N11" s="180"/>
+      <c r="O11" s="180"/>
+      <c r="P11" s="180"/>
+      <c r="Q11" s="180"/>
+      <c r="R11" s="180"/>
       <c r="S11" s="23"/>
     </row>
     <row r="12" spans="1:21" s="10" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.2">
@@ -3553,37 +3585,37 @@
       <c r="S12" s="29"/>
     </row>
     <row r="13" spans="1:21" s="10" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="181" t="s">
+      <c r="A13" s="191" t="s">
         <v>44</v>
       </c>
-      <c r="B13" s="137"/>
-      <c r="C13" s="137"/>
-      <c r="D13" s="137"/>
-      <c r="E13" s="137"/>
-      <c r="F13" s="137"/>
-      <c r="G13" s="183" t="s">
+      <c r="B13" s="192"/>
+      <c r="C13" s="192"/>
+      <c r="D13" s="192"/>
+      <c r="E13" s="192"/>
+      <c r="F13" s="192"/>
+      <c r="G13" s="195" t="s">
         <v>69</v>
       </c>
-      <c r="H13" s="184"/>
-      <c r="I13" s="184"/>
-      <c r="J13" s="184"/>
-      <c r="K13" s="184"/>
-      <c r="L13" s="184"/>
-      <c r="M13" s="184"/>
-      <c r="N13" s="184"/>
-      <c r="O13" s="184"/>
-      <c r="P13" s="184"/>
-      <c r="Q13" s="184"/>
-      <c r="R13" s="184"/>
-      <c r="S13" s="185"/>
+      <c r="H13" s="196"/>
+      <c r="I13" s="196"/>
+      <c r="J13" s="196"/>
+      <c r="K13" s="196"/>
+      <c r="L13" s="196"/>
+      <c r="M13" s="196"/>
+      <c r="N13" s="196"/>
+      <c r="O13" s="196"/>
+      <c r="P13" s="196"/>
+      <c r="Q13" s="196"/>
+      <c r="R13" s="196"/>
+      <c r="S13" s="197"/>
     </row>
     <row r="14" spans="1:21" s="10" customFormat="1" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="182"/>
-      <c r="B14" s="182"/>
-      <c r="C14" s="182"/>
-      <c r="D14" s="182"/>
-      <c r="E14" s="182"/>
-      <c r="F14" s="174"/>
+      <c r="A14" s="194"/>
+      <c r="B14" s="194"/>
+      <c r="C14" s="194"/>
+      <c r="D14" s="194"/>
+      <c r="E14" s="194"/>
+      <c r="F14" s="184"/>
       <c r="G14" s="67"/>
       <c r="H14" s="15"/>
       <c r="I14" s="15"/>
@@ -3591,7 +3623,7 @@
       <c r="K14" s="15"/>
       <c r="L14" s="15"/>
       <c r="M14" s="15"/>
-      <c r="N14" s="140" t="s">
+      <c r="N14" s="198" t="s">
         <v>80</v>
       </c>
       <c r="O14" s="15"/>
@@ -3601,12 +3633,12 @@
       <c r="S14" s="60"/>
     </row>
     <row r="15" spans="1:21" s="10" customFormat="1" ht="36.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="174"/>
-      <c r="B15" s="175"/>
-      <c r="C15" s="175"/>
-      <c r="D15" s="175"/>
-      <c r="E15" s="175"/>
-      <c r="F15" s="175"/>
+      <c r="A15" s="184"/>
+      <c r="B15" s="185"/>
+      <c r="C15" s="185"/>
+      <c r="D15" s="185"/>
+      <c r="E15" s="185"/>
+      <c r="F15" s="185"/>
       <c r="G15" s="64" t="s">
         <v>79</v>
       </c>
@@ -3618,7 +3650,7 @@
       </c>
       <c r="L15" s="66"/>
       <c r="M15" s="65"/>
-      <c r="N15" s="186"/>
+      <c r="N15" s="199"/>
       <c r="O15" s="66"/>
       <c r="P15" s="65"/>
       <c r="Q15" s="65"/>
@@ -3626,14 +3658,14 @@
       <c r="S15" s="61"/>
     </row>
     <row r="16" spans="1:21" s="7" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="145" t="s">
+      <c r="A16" s="210" t="s">
         <v>45</v>
       </c>
-      <c r="B16" s="146"/>
-      <c r="C16" s="147"/>
-      <c r="D16" s="147"/>
-      <c r="E16" s="147"/>
-      <c r="F16" s="147"/>
+      <c r="B16" s="211"/>
+      <c r="C16" s="212"/>
+      <c r="D16" s="212"/>
+      <c r="E16" s="212"/>
+      <c r="F16" s="212"/>
       <c r="G16" s="15"/>
       <c r="H16" s="15"/>
       <c r="I16" s="15"/>
@@ -3655,35 +3687,35 @@
       <c r="B17" s="62" t="s">
         <v>31</v>
       </c>
-      <c r="C17" s="119" t="s">
+      <c r="C17" s="178" t="s">
         <v>32</v>
       </c>
-      <c r="D17" s="120"/>
-      <c r="E17" s="119" t="s">
+      <c r="D17" s="225"/>
+      <c r="E17" s="178" t="s">
         <v>33</v>
       </c>
-      <c r="F17" s="168"/>
-      <c r="G17" s="169"/>
-      <c r="H17" s="163"/>
+      <c r="F17" s="179"/>
+      <c r="G17" s="138"/>
+      <c r="H17" s="136"/>
       <c r="I17" s="63" t="s">
         <v>35</v>
       </c>
-      <c r="J17" s="129" t="s">
+      <c r="J17" s="230" t="s">
         <v>34</v>
       </c>
-      <c r="K17" s="130"/>
-      <c r="L17" s="130"/>
-      <c r="M17" s="130"/>
-      <c r="N17" s="131"/>
-      <c r="O17" s="162" t="s">
+      <c r="K17" s="231"/>
+      <c r="L17" s="231"/>
+      <c r="M17" s="231"/>
+      <c r="N17" s="232"/>
+      <c r="O17" s="170" t="s">
         <v>67</v>
       </c>
-      <c r="P17" s="163"/>
-      <c r="Q17" s="171" t="s">
+      <c r="P17" s="136"/>
+      <c r="Q17" s="181" t="s">
         <v>68</v>
       </c>
-      <c r="R17" s="172"/>
-      <c r="S17" s="173"/>
+      <c r="R17" s="182"/>
+      <c r="S17" s="183"/>
     </row>
     <row r="18" spans="1:19" s="36" customFormat="1" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A18" s="33" t="s">
@@ -3692,207 +3724,207 @@
       <c r="B18" s="33" t="s">
         <v>17</v>
       </c>
-      <c r="C18" s="81" t="s">
+      <c r="C18" s="193" t="s">
         <v>18</v>
       </c>
-      <c r="D18" s="81"/>
-      <c r="E18" s="114" t="s">
+      <c r="D18" s="193"/>
+      <c r="E18" s="164" t="s">
         <v>19</v>
       </c>
-      <c r="F18" s="81"/>
-      <c r="G18" s="81"/>
-      <c r="H18" s="115"/>
+      <c r="F18" s="193"/>
+      <c r="G18" s="193"/>
+      <c r="H18" s="165"/>
       <c r="I18" s="34" t="s">
         <v>49</v>
       </c>
-      <c r="J18" s="164" t="s">
+      <c r="J18" s="171" t="s">
         <v>46</v>
       </c>
-      <c r="K18" s="167"/>
-      <c r="L18" s="164" t="s">
+      <c r="K18" s="177"/>
+      <c r="L18" s="171" t="s">
         <v>47</v>
       </c>
-      <c r="M18" s="165"/>
+      <c r="M18" s="172"/>
       <c r="N18" s="35" t="s">
         <v>48</v>
       </c>
-      <c r="O18" s="114" t="s">
+      <c r="O18" s="164" t="s">
         <v>50</v>
       </c>
-      <c r="P18" s="115"/>
-      <c r="Q18" s="114" t="s">
+      <c r="P18" s="165"/>
+      <c r="Q18" s="164" t="s">
         <v>20</v>
       </c>
-      <c r="R18" s="81"/>
-      <c r="S18" s="115"/>
+      <c r="R18" s="193"/>
+      <c r="S18" s="165"/>
     </row>
     <row r="19" spans="1:19" s="9" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A19" s="37"/>
       <c r="B19" s="38"/>
-      <c r="C19" s="124"/>
-      <c r="D19" s="125"/>
-      <c r="E19" s="99"/>
-      <c r="F19" s="100"/>
-      <c r="G19" s="100"/>
-      <c r="H19" s="101"/>
+      <c r="C19" s="175"/>
+      <c r="D19" s="176"/>
+      <c r="E19" s="226"/>
+      <c r="F19" s="157"/>
+      <c r="G19" s="157"/>
+      <c r="H19" s="159"/>
       <c r="I19" s="40"/>
-      <c r="J19" s="97"/>
-      <c r="K19" s="98"/>
-      <c r="L19" s="97"/>
-      <c r="M19" s="98"/>
+      <c r="J19" s="84"/>
+      <c r="K19" s="86"/>
+      <c r="L19" s="84"/>
+      <c r="M19" s="86"/>
       <c r="N19" s="41"/>
-      <c r="O19" s="97"/>
-      <c r="P19" s="98"/>
-      <c r="Q19" s="97">
+      <c r="O19" s="84"/>
+      <c r="P19" s="86"/>
+      <c r="Q19" s="84">
         <f>SUM(J19:O19)</f>
         <v>0</v>
       </c>
-      <c r="R19" s="143"/>
-      <c r="S19" s="98"/>
+      <c r="R19" s="85"/>
+      <c r="S19" s="86"/>
     </row>
     <row r="20" spans="1:19" s="9" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A20" s="42"/>
       <c r="B20" s="39"/>
-      <c r="C20" s="124"/>
-      <c r="D20" s="125"/>
-      <c r="E20" s="99"/>
-      <c r="F20" s="100"/>
-      <c r="G20" s="100"/>
-      <c r="H20" s="101"/>
+      <c r="C20" s="175"/>
+      <c r="D20" s="176"/>
+      <c r="E20" s="226"/>
+      <c r="F20" s="157"/>
+      <c r="G20" s="157"/>
+      <c r="H20" s="159"/>
       <c r="I20" s="40"/>
-      <c r="J20" s="97"/>
-      <c r="K20" s="98"/>
-      <c r="L20" s="97"/>
-      <c r="M20" s="98"/>
+      <c r="J20" s="84"/>
+      <c r="K20" s="86"/>
+      <c r="L20" s="84"/>
+      <c r="M20" s="86"/>
       <c r="N20" s="43"/>
-      <c r="O20" s="97"/>
-      <c r="P20" s="98"/>
-      <c r="Q20" s="97">
+      <c r="O20" s="84"/>
+      <c r="P20" s="86"/>
+      <c r="Q20" s="84">
         <f t="shared" ref="Q20:Q25" si="0">SUM(J20:O20)</f>
         <v>0</v>
       </c>
-      <c r="R20" s="143"/>
-      <c r="S20" s="98"/>
+      <c r="R20" s="85"/>
+      <c r="S20" s="86"/>
     </row>
     <row r="21" spans="1:19" s="9" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A21" s="42"/>
       <c r="B21" s="39"/>
-      <c r="C21" s="124"/>
-      <c r="D21" s="125"/>
-      <c r="E21" s="99"/>
-      <c r="F21" s="100"/>
-      <c r="G21" s="100"/>
-      <c r="H21" s="101"/>
+      <c r="C21" s="175"/>
+      <c r="D21" s="176"/>
+      <c r="E21" s="226"/>
+      <c r="F21" s="157"/>
+      <c r="G21" s="157"/>
+      <c r="H21" s="159"/>
       <c r="I21" s="40"/>
-      <c r="J21" s="97"/>
-      <c r="K21" s="98"/>
-      <c r="L21" s="97"/>
-      <c r="M21" s="98"/>
+      <c r="J21" s="84"/>
+      <c r="K21" s="86"/>
+      <c r="L21" s="84"/>
+      <c r="M21" s="86"/>
       <c r="N21" s="43"/>
-      <c r="O21" s="97"/>
-      <c r="P21" s="98"/>
-      <c r="Q21" s="97">
+      <c r="O21" s="84"/>
+      <c r="P21" s="86"/>
+      <c r="Q21" s="84">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="R21" s="143"/>
-      <c r="S21" s="98"/>
+      <c r="R21" s="85"/>
+      <c r="S21" s="86"/>
     </row>
     <row r="22" spans="1:19" s="9" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A22" s="42"/>
       <c r="B22" s="39"/>
-      <c r="C22" s="124"/>
-      <c r="D22" s="125"/>
-      <c r="E22" s="99"/>
-      <c r="F22" s="100"/>
-      <c r="G22" s="100"/>
-      <c r="H22" s="101"/>
+      <c r="C22" s="175"/>
+      <c r="D22" s="176"/>
+      <c r="E22" s="226"/>
+      <c r="F22" s="157"/>
+      <c r="G22" s="157"/>
+      <c r="H22" s="159"/>
       <c r="I22" s="40"/>
-      <c r="J22" s="97"/>
-      <c r="K22" s="98"/>
-      <c r="L22" s="97"/>
-      <c r="M22" s="98"/>
+      <c r="J22" s="84"/>
+      <c r="K22" s="86"/>
+      <c r="L22" s="84"/>
+      <c r="M22" s="86"/>
       <c r="N22" s="43"/>
-      <c r="O22" s="97"/>
-      <c r="P22" s="98"/>
-      <c r="Q22" s="97">
+      <c r="O22" s="84"/>
+      <c r="P22" s="86"/>
+      <c r="Q22" s="84">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="R22" s="143"/>
-      <c r="S22" s="98"/>
+      <c r="R22" s="85"/>
+      <c r="S22" s="86"/>
     </row>
     <row r="23" spans="1:19" s="9" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A23" s="42"/>
       <c r="B23" s="39"/>
-      <c r="C23" s="124"/>
-      <c r="D23" s="125"/>
-      <c r="E23" s="128"/>
-      <c r="F23" s="100"/>
-      <c r="G23" s="100"/>
-      <c r="H23" s="101"/>
+      <c r="C23" s="175"/>
+      <c r="D23" s="176"/>
+      <c r="E23" s="156"/>
+      <c r="F23" s="157"/>
+      <c r="G23" s="157"/>
+      <c r="H23" s="159"/>
       <c r="I23" s="40"/>
-      <c r="J23" s="97"/>
-      <c r="K23" s="98"/>
-      <c r="L23" s="97"/>
-      <c r="M23" s="98"/>
+      <c r="J23" s="84"/>
+      <c r="K23" s="86"/>
+      <c r="L23" s="84"/>
+      <c r="M23" s="86"/>
       <c r="N23" s="43"/>
-      <c r="O23" s="97"/>
-      <c r="P23" s="98"/>
-      <c r="Q23" s="97">
+      <c r="O23" s="84"/>
+      <c r="P23" s="86"/>
+      <c r="Q23" s="84">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="R23" s="143"/>
-      <c r="S23" s="98"/>
+      <c r="R23" s="85"/>
+      <c r="S23" s="86"/>
     </row>
     <row r="24" spans="1:19" s="9" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A24" s="42"/>
       <c r="B24" s="39"/>
-      <c r="C24" s="124"/>
-      <c r="D24" s="125"/>
-      <c r="E24" s="128"/>
-      <c r="F24" s="100"/>
-      <c r="G24" s="100"/>
-      <c r="H24" s="101"/>
+      <c r="C24" s="175"/>
+      <c r="D24" s="176"/>
+      <c r="E24" s="156"/>
+      <c r="F24" s="157"/>
+      <c r="G24" s="157"/>
+      <c r="H24" s="159"/>
       <c r="I24" s="40"/>
-      <c r="J24" s="97"/>
-      <c r="K24" s="98"/>
-      <c r="L24" s="97"/>
-      <c r="M24" s="98"/>
+      <c r="J24" s="84"/>
+      <c r="K24" s="86"/>
+      <c r="L24" s="84"/>
+      <c r="M24" s="86"/>
       <c r="N24" s="43"/>
-      <c r="O24" s="97"/>
-      <c r="P24" s="98"/>
-      <c r="Q24" s="97">
+      <c r="O24" s="84"/>
+      <c r="P24" s="86"/>
+      <c r="Q24" s="84">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="R24" s="143"/>
-      <c r="S24" s="98"/>
+      <c r="R24" s="85"/>
+      <c r="S24" s="86"/>
     </row>
     <row r="25" spans="1:19" s="9" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A25" s="44"/>
       <c r="B25" s="45"/>
-      <c r="C25" s="126"/>
-      <c r="D25" s="127"/>
-      <c r="E25" s="128"/>
-      <c r="F25" s="100"/>
-      <c r="G25" s="100"/>
-      <c r="H25" s="101"/>
+      <c r="C25" s="228"/>
+      <c r="D25" s="229"/>
+      <c r="E25" s="156"/>
+      <c r="F25" s="157"/>
+      <c r="G25" s="157"/>
+      <c r="H25" s="159"/>
       <c r="I25" s="40"/>
-      <c r="J25" s="97"/>
-      <c r="K25" s="98"/>
-      <c r="L25" s="97"/>
-      <c r="M25" s="98"/>
+      <c r="J25" s="84"/>
+      <c r="K25" s="86"/>
+      <c r="L25" s="84"/>
+      <c r="M25" s="86"/>
       <c r="N25" s="43"/>
-      <c r="O25" s="97"/>
-      <c r="P25" s="98"/>
-      <c r="Q25" s="97">
+      <c r="O25" s="84"/>
+      <c r="P25" s="86"/>
+      <c r="Q25" s="84">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="R25" s="143"/>
-      <c r="S25" s="98"/>
+      <c r="R25" s="85"/>
+      <c r="S25" s="86"/>
     </row>
     <row r="26" spans="1:19" s="1" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="3"/>
@@ -3901,225 +3933,225 @@
       <c r="D26" s="4"/>
       <c r="E26" s="4"/>
       <c r="F26" s="5"/>
-      <c r="G26" s="123" t="s">
+      <c r="G26" s="227" t="s">
         <v>26</v>
       </c>
-      <c r="H26" s="123"/>
+      <c r="H26" s="227"/>
       <c r="I26" s="2">
         <f>SUM(I19:I25)</f>
         <v>0</v>
       </c>
-      <c r="J26" s="121">
+      <c r="J26" s="154">
         <f>SUM(J19:K25)</f>
         <v>0</v>
       </c>
-      <c r="K26" s="122"/>
-      <c r="L26" s="121">
+      <c r="K26" s="155"/>
+      <c r="L26" s="154">
         <f>SUM(L19:M25)</f>
         <v>0</v>
       </c>
-      <c r="M26" s="122"/>
+      <c r="M26" s="155"/>
       <c r="N26" s="6">
         <f>SUM(N19:N25)</f>
         <v>0</v>
       </c>
-      <c r="O26" s="121">
+      <c r="O26" s="154">
         <f>SUM(O19:P25)</f>
         <v>0</v>
       </c>
-      <c r="P26" s="122"/>
-      <c r="Q26" s="200">
+      <c r="P26" s="155"/>
+      <c r="Q26" s="151">
         <f>SUM(Q19:S25)</f>
         <v>0</v>
       </c>
-      <c r="R26" s="201"/>
-      <c r="S26" s="202"/>
+      <c r="R26" s="152"/>
+      <c r="S26" s="153"/>
     </row>
     <row r="27" spans="1:19" s="46" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="116" t="s">
+      <c r="A27" s="222" t="s">
         <v>27</v>
       </c>
-      <c r="B27" s="117"/>
-      <c r="C27" s="117"/>
-      <c r="D27" s="118"/>
+      <c r="B27" s="223"/>
+      <c r="C27" s="223"/>
+      <c r="D27" s="224"/>
       <c r="E27" s="30" t="s">
         <v>14</v>
       </c>
-      <c r="F27" s="189" t="s">
+      <c r="F27" s="135" t="s">
         <v>15</v>
       </c>
-      <c r="G27" s="169"/>
-      <c r="H27" s="169"/>
-      <c r="I27" s="169"/>
-      <c r="J27" s="169"/>
-      <c r="K27" s="169"/>
-      <c r="L27" s="189" t="s">
+      <c r="G27" s="138"/>
+      <c r="H27" s="138"/>
+      <c r="I27" s="138"/>
+      <c r="J27" s="138"/>
+      <c r="K27" s="138"/>
+      <c r="L27" s="135" t="s">
         <v>36</v>
       </c>
-      <c r="M27" s="163"/>
+      <c r="M27" s="136"/>
       <c r="N27" s="30" t="s">
         <v>40</v>
       </c>
-      <c r="O27" s="189" t="s">
+      <c r="O27" s="135" t="s">
         <v>37</v>
       </c>
-      <c r="P27" s="163"/>
+      <c r="P27" s="136"/>
       <c r="Q27" s="31" t="s">
         <v>38</v>
       </c>
-      <c r="R27" s="189" t="s">
+      <c r="R27" s="135" t="s">
         <v>41</v>
       </c>
-      <c r="S27" s="163"/>
+      <c r="S27" s="136"/>
     </row>
     <row r="28" spans="1:19" s="46" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="95" t="s">
+      <c r="A28" s="233" t="s">
         <v>21</v>
       </c>
-      <c r="B28" s="80" t="s">
+      <c r="B28" s="242" t="s">
         <v>22</v>
       </c>
-      <c r="C28" s="80" t="s">
+      <c r="C28" s="242" t="s">
         <v>16</v>
       </c>
-      <c r="D28" s="82"/>
-      <c r="E28" s="84" t="s">
+      <c r="D28" s="243"/>
+      <c r="E28" s="245" t="s">
         <v>11</v>
       </c>
-      <c r="F28" s="88" t="s">
+      <c r="F28" s="247" t="s">
         <v>54</v>
       </c>
-      <c r="G28" s="89"/>
-      <c r="H28" s="89"/>
-      <c r="I28" s="89"/>
-      <c r="J28" s="89"/>
-      <c r="K28" s="90"/>
-      <c r="L28" s="106" t="s">
+      <c r="G28" s="248"/>
+      <c r="H28" s="248"/>
+      <c r="I28" s="248"/>
+      <c r="J28" s="248"/>
+      <c r="K28" s="249"/>
+      <c r="L28" s="236" t="s">
         <v>43</v>
       </c>
-      <c r="M28" s="107"/>
-      <c r="N28" s="110" t="s">
+      <c r="M28" s="237"/>
+      <c r="N28" s="240" t="s">
         <v>82</v>
       </c>
-      <c r="O28" s="112" t="s">
-        <v>107</v>
-      </c>
-      <c r="P28" s="113"/>
-      <c r="Q28" s="187" t="s">
+      <c r="O28" s="241" t="s">
+        <v>106</v>
+      </c>
+      <c r="P28" s="163"/>
+      <c r="Q28" s="160" t="s">
         <v>56</v>
       </c>
-      <c r="R28" s="188" t="s">
+      <c r="R28" s="162" t="s">
         <v>16</v>
       </c>
-      <c r="S28" s="113"/>
+      <c r="S28" s="163"/>
     </row>
     <row r="29" spans="1:19" s="36" customFormat="1" ht="36.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="96"/>
-      <c r="B29" s="81"/>
-      <c r="C29" s="81"/>
-      <c r="D29" s="83"/>
-      <c r="E29" s="85"/>
-      <c r="F29" s="91"/>
-      <c r="G29" s="92"/>
-      <c r="H29" s="92"/>
-      <c r="I29" s="92"/>
-      <c r="J29" s="92"/>
-      <c r="K29" s="93"/>
-      <c r="L29" s="108"/>
-      <c r="M29" s="109"/>
-      <c r="N29" s="111"/>
-      <c r="O29" s="114"/>
-      <c r="P29" s="115"/>
-      <c r="Q29" s="111"/>
-      <c r="R29" s="114"/>
-      <c r="S29" s="115"/>
+      <c r="A29" s="234"/>
+      <c r="B29" s="193"/>
+      <c r="C29" s="193"/>
+      <c r="D29" s="244"/>
+      <c r="E29" s="246"/>
+      <c r="F29" s="250"/>
+      <c r="G29" s="251"/>
+      <c r="H29" s="251"/>
+      <c r="I29" s="251"/>
+      <c r="J29" s="251"/>
+      <c r="K29" s="252"/>
+      <c r="L29" s="238"/>
+      <c r="M29" s="239"/>
+      <c r="N29" s="161"/>
+      <c r="O29" s="164"/>
+      <c r="P29" s="165"/>
+      <c r="Q29" s="161"/>
+      <c r="R29" s="164"/>
+      <c r="S29" s="165"/>
     </row>
     <row r="30" spans="1:19" s="9" customFormat="1" ht="15" x14ac:dyDescent="0.2">
-      <c r="A30" s="37"/>
+      <c r="A30" s="49"/>
       <c r="B30" s="50"/>
       <c r="C30" s="78"/>
       <c r="D30" s="79"/>
       <c r="E30" s="51"/>
-      <c r="F30" s="94"/>
-      <c r="G30" s="87"/>
-      <c r="H30" s="87"/>
-      <c r="I30" s="87"/>
-      <c r="J30" s="87"/>
-      <c r="K30" s="87"/>
-      <c r="L30" s="104"/>
-      <c r="M30" s="105"/>
+      <c r="F30" s="147"/>
+      <c r="G30" s="148"/>
+      <c r="H30" s="148"/>
+      <c r="I30" s="148"/>
+      <c r="J30" s="148"/>
+      <c r="K30" s="148"/>
+      <c r="L30" s="96"/>
+      <c r="M30" s="97"/>
       <c r="N30" s="52"/>
-      <c r="O30" s="102">
-        <f>L30-N30</f>
+      <c r="O30" s="80">
+        <f t="shared" ref="O30:O31" si="1">L30-N30</f>
         <v>0</v>
       </c>
-      <c r="P30" s="103"/>
-      <c r="Q30" s="58">
-        <v>0.72499999999999998</v>
-      </c>
-      <c r="R30" s="97">
-        <f>(ROUND(+O30*Q30,2))</f>
+      <c r="P30" s="81"/>
+      <c r="Q30" s="257">
+        <v>0.76</v>
+      </c>
+      <c r="R30" s="84">
+        <f t="shared" ref="R30:R31" si="2">(ROUND(+O30*Q30,2))</f>
         <v>0</v>
       </c>
-      <c r="S30" s="98"/>
-    </row>
-    <row r="31" spans="1:19" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="42"/>
+      <c r="S30" s="86"/>
+    </row>
+    <row r="31" spans="1:19" s="9" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A31" s="49"/>
       <c r="B31" s="50"/>
       <c r="C31" s="78"/>
       <c r="D31" s="79"/>
       <c r="E31" s="51"/>
-      <c r="F31" s="94"/>
-      <c r="G31" s="87"/>
-      <c r="H31" s="87"/>
-      <c r="I31" s="87"/>
-      <c r="J31" s="87"/>
-      <c r="K31" s="87"/>
-      <c r="L31" s="104"/>
-      <c r="M31" s="105"/>
+      <c r="F31" s="147"/>
+      <c r="G31" s="148"/>
+      <c r="H31" s="148"/>
+      <c r="I31" s="148"/>
+      <c r="J31" s="148"/>
+      <c r="K31" s="148"/>
+      <c r="L31" s="96"/>
+      <c r="M31" s="97"/>
       <c r="N31" s="52"/>
-      <c r="O31" s="102">
-        <f t="shared" ref="O31:O33" si="1">L31-N31</f>
+      <c r="O31" s="80">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="P31" s="103"/>
-      <c r="Q31" s="58">
-        <v>0.20499999999999999</v>
-      </c>
-      <c r="R31" s="97">
-        <f t="shared" ref="R31:R33" si="2">(ROUND(+O31*Q31,2))</f>
+      <c r="P31" s="81"/>
+      <c r="Q31" s="257">
+        <v>0.23499999999999999</v>
+      </c>
+      <c r="R31" s="84">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="S31" s="98"/>
-    </row>
-    <row r="32" spans="1:19" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="42"/>
+      <c r="S31" s="86"/>
+    </row>
+    <row r="32" spans="1:19" s="9" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A32" s="37"/>
       <c r="B32" s="50"/>
       <c r="C32" s="78"/>
       <c r="D32" s="79"/>
       <c r="E32" s="51"/>
-      <c r="F32" s="94"/>
-      <c r="G32" s="87"/>
-      <c r="H32" s="87"/>
-      <c r="I32" s="87"/>
-      <c r="J32" s="87"/>
-      <c r="K32" s="87"/>
-      <c r="L32" s="104"/>
-      <c r="M32" s="105"/>
+      <c r="F32" s="235"/>
+      <c r="G32" s="148"/>
+      <c r="H32" s="148"/>
+      <c r="I32" s="148"/>
+      <c r="J32" s="148"/>
+      <c r="K32" s="148"/>
+      <c r="L32" s="96"/>
+      <c r="M32" s="97"/>
       <c r="N32" s="52"/>
-      <c r="O32" s="102">
-        <f t="shared" si="1"/>
+      <c r="O32" s="80">
+        <f>L32-N32</f>
         <v>0</v>
       </c>
-      <c r="P32" s="103"/>
+      <c r="P32" s="81"/>
       <c r="Q32" s="58">
-        <v>0.7</v>
-      </c>
-      <c r="R32" s="97">
-        <f t="shared" si="2"/>
+        <v>0.72499999999999998</v>
+      </c>
+      <c r="R32" s="84">
+        <f>(ROUND(+O32*Q32,2))</f>
         <v>0</v>
       </c>
-      <c r="S32" s="98"/>
+      <c r="S32" s="86"/>
     </row>
     <row r="33" spans="1:19" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="42"/>
@@ -4127,112 +4159,128 @@
       <c r="C33" s="78"/>
       <c r="D33" s="79"/>
       <c r="E33" s="51"/>
-      <c r="F33" s="94"/>
-      <c r="G33" s="87"/>
-      <c r="H33" s="87"/>
-      <c r="I33" s="87"/>
-      <c r="J33" s="87"/>
-      <c r="K33" s="87"/>
-      <c r="L33" s="104"/>
-      <c r="M33" s="105"/>
+      <c r="F33" s="235"/>
+      <c r="G33" s="148"/>
+      <c r="H33" s="148"/>
+      <c r="I33" s="148"/>
+      <c r="J33" s="148"/>
+      <c r="K33" s="148"/>
+      <c r="L33" s="96"/>
+      <c r="M33" s="97"/>
       <c r="N33" s="52"/>
-      <c r="O33" s="102">
-        <f t="shared" si="1"/>
+      <c r="O33" s="80">
+        <f t="shared" ref="O33:O35" si="3">L33-N33</f>
         <v>0</v>
       </c>
-      <c r="P33" s="103"/>
+      <c r="P33" s="81"/>
       <c r="Q33" s="58">
-        <v>0.21</v>
-      </c>
-      <c r="R33" s="97">
-        <f t="shared" si="2"/>
+        <v>0.20499999999999999</v>
+      </c>
+      <c r="R33" s="84">
+        <f t="shared" ref="R33:R35" si="4">(ROUND(+O33*Q33,2))</f>
         <v>0</v>
       </c>
-      <c r="S33" s="98"/>
+      <c r="S33" s="86"/>
     </row>
     <row r="34" spans="1:19" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="49"/>
+      <c r="A34" s="42"/>
       <c r="B34" s="50"/>
       <c r="C34" s="78"/>
       <c r="D34" s="79"/>
       <c r="E34" s="51"/>
-      <c r="F34" s="94"/>
-      <c r="G34" s="87"/>
-      <c r="H34" s="87"/>
-      <c r="I34" s="87"/>
-      <c r="J34" s="87"/>
-      <c r="K34" s="87"/>
-      <c r="L34" s="104"/>
-      <c r="M34" s="105"/>
+      <c r="F34" s="235"/>
+      <c r="G34" s="148"/>
+      <c r="H34" s="148"/>
+      <c r="I34" s="148"/>
+      <c r="J34" s="148"/>
+      <c r="K34" s="148"/>
+      <c r="L34" s="96"/>
+      <c r="M34" s="97"/>
       <c r="N34" s="52"/>
-      <c r="O34" s="102"/>
-      <c r="P34" s="103"/>
-      <c r="Q34" s="58"/>
-      <c r="R34" s="97"/>
-      <c r="S34" s="98"/>
+      <c r="O34" s="80">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="P34" s="81"/>
+      <c r="Q34" s="58">
+        <v>0.7</v>
+      </c>
+      <c r="R34" s="84">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="S34" s="86"/>
     </row>
     <row r="35" spans="1:19" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="49"/>
+      <c r="A35" s="42"/>
       <c r="B35" s="50"/>
       <c r="C35" s="78"/>
       <c r="D35" s="79"/>
       <c r="E35" s="51"/>
-      <c r="F35" s="94"/>
-      <c r="G35" s="87"/>
-      <c r="H35" s="87"/>
-      <c r="I35" s="87"/>
-      <c r="J35" s="87"/>
-      <c r="K35" s="87"/>
-      <c r="L35" s="104"/>
-      <c r="M35" s="105"/>
+      <c r="F35" s="235"/>
+      <c r="G35" s="148"/>
+      <c r="H35" s="148"/>
+      <c r="I35" s="148"/>
+      <c r="J35" s="148"/>
+      <c r="K35" s="148"/>
+      <c r="L35" s="96"/>
+      <c r="M35" s="97"/>
       <c r="N35" s="52"/>
-      <c r="O35" s="102"/>
-      <c r="P35" s="103"/>
-      <c r="Q35" s="58"/>
-      <c r="R35" s="97"/>
-      <c r="S35" s="98"/>
-    </row>
-    <row r="36" spans="1:19" s="9" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="O35" s="80">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="P35" s="81"/>
+      <c r="Q35" s="58">
+        <v>0.21</v>
+      </c>
+      <c r="R35" s="84">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="S35" s="86"/>
+    </row>
+    <row r="36" spans="1:19" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="49"/>
       <c r="B36" s="50"/>
       <c r="C36" s="78"/>
       <c r="D36" s="79"/>
       <c r="E36" s="51"/>
-      <c r="F36" s="94"/>
-      <c r="G36" s="87"/>
-      <c r="H36" s="87"/>
-      <c r="I36" s="87"/>
-      <c r="J36" s="87"/>
-      <c r="K36" s="87"/>
-      <c r="L36" s="104"/>
-      <c r="M36" s="105"/>
+      <c r="F36" s="235"/>
+      <c r="G36" s="148"/>
+      <c r="H36" s="148"/>
+      <c r="I36" s="148"/>
+      <c r="J36" s="148"/>
+      <c r="K36" s="148"/>
+      <c r="L36" s="96"/>
+      <c r="M36" s="97"/>
       <c r="N36" s="52"/>
-      <c r="O36" s="102"/>
-      <c r="P36" s="103"/>
+      <c r="O36" s="80"/>
+      <c r="P36" s="81"/>
       <c r="Q36" s="58"/>
-      <c r="R36" s="97"/>
-      <c r="S36" s="98"/>
-    </row>
-    <row r="37" spans="1:19" s="9" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="R36" s="84"/>
+      <c r="S36" s="86"/>
+    </row>
+    <row r="37" spans="1:19" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="49"/>
       <c r="B37" s="50"/>
       <c r="C37" s="78"/>
       <c r="D37" s="79"/>
       <c r="E37" s="51"/>
-      <c r="F37" s="94"/>
-      <c r="G37" s="87"/>
-      <c r="H37" s="87"/>
-      <c r="I37" s="87"/>
-      <c r="J37" s="87"/>
-      <c r="K37" s="87"/>
-      <c r="L37" s="104"/>
-      <c r="M37" s="105"/>
+      <c r="F37" s="235"/>
+      <c r="G37" s="148"/>
+      <c r="H37" s="148"/>
+      <c r="I37" s="148"/>
+      <c r="J37" s="148"/>
+      <c r="K37" s="148"/>
+      <c r="L37" s="96"/>
+      <c r="M37" s="97"/>
       <c r="N37" s="52"/>
-      <c r="O37" s="102"/>
-      <c r="P37" s="103"/>
+      <c r="O37" s="80"/>
+      <c r="P37" s="81"/>
       <c r="Q37" s="58"/>
-      <c r="R37" s="97"/>
-      <c r="S37" s="98"/>
+      <c r="R37" s="84"/>
+      <c r="S37" s="86"/>
     </row>
     <row r="38" spans="1:19" s="9" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A38" s="49"/>
@@ -4240,20 +4288,20 @@
       <c r="C38" s="78"/>
       <c r="D38" s="79"/>
       <c r="E38" s="51"/>
-      <c r="F38" s="86"/>
-      <c r="G38" s="87"/>
-      <c r="H38" s="87"/>
-      <c r="I38" s="87"/>
-      <c r="J38" s="87"/>
-      <c r="K38" s="87"/>
-      <c r="L38" s="104"/>
-      <c r="M38" s="105"/>
+      <c r="F38" s="235"/>
+      <c r="G38" s="148"/>
+      <c r="H38" s="148"/>
+      <c r="I38" s="148"/>
+      <c r="J38" s="148"/>
+      <c r="K38" s="148"/>
+      <c r="L38" s="96"/>
+      <c r="M38" s="97"/>
       <c r="N38" s="52"/>
-      <c r="O38" s="102"/>
-      <c r="P38" s="103"/>
-      <c r="Q38" s="56"/>
-      <c r="R38" s="97"/>
-      <c r="S38" s="98"/>
+      <c r="O38" s="80"/>
+      <c r="P38" s="81"/>
+      <c r="Q38" s="58"/>
+      <c r="R38" s="84"/>
+      <c r="S38" s="86"/>
     </row>
     <row r="39" spans="1:19" s="9" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A39" s="49"/>
@@ -4261,20 +4309,20 @@
       <c r="C39" s="78"/>
       <c r="D39" s="79"/>
       <c r="E39" s="51"/>
-      <c r="F39" s="86"/>
-      <c r="G39" s="87"/>
-      <c r="H39" s="87"/>
-      <c r="I39" s="87"/>
-      <c r="J39" s="87"/>
-      <c r="K39" s="87"/>
-      <c r="L39" s="104"/>
-      <c r="M39" s="105"/>
+      <c r="F39" s="235"/>
+      <c r="G39" s="148"/>
+      <c r="H39" s="148"/>
+      <c r="I39" s="148"/>
+      <c r="J39" s="148"/>
+      <c r="K39" s="148"/>
+      <c r="L39" s="96"/>
+      <c r="M39" s="97"/>
       <c r="N39" s="52"/>
-      <c r="O39" s="102"/>
-      <c r="P39" s="103"/>
-      <c r="Q39" s="57"/>
-      <c r="R39" s="97"/>
-      <c r="S39" s="98"/>
+      <c r="O39" s="80"/>
+      <c r="P39" s="81"/>
+      <c r="Q39" s="58"/>
+      <c r="R39" s="84"/>
+      <c r="S39" s="86"/>
     </row>
     <row r="40" spans="1:19" s="9" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A40" s="49"/>
@@ -4282,20 +4330,20 @@
       <c r="C40" s="78"/>
       <c r="D40" s="79"/>
       <c r="E40" s="51"/>
-      <c r="F40" s="86"/>
-      <c r="G40" s="87"/>
-      <c r="H40" s="87"/>
-      <c r="I40" s="87"/>
-      <c r="J40" s="87"/>
-      <c r="K40" s="87"/>
-      <c r="L40" s="104"/>
-      <c r="M40" s="105"/>
+      <c r="F40" s="147"/>
+      <c r="G40" s="148"/>
+      <c r="H40" s="148"/>
+      <c r="I40" s="148"/>
+      <c r="J40" s="148"/>
+      <c r="K40" s="148"/>
+      <c r="L40" s="96"/>
+      <c r="M40" s="97"/>
       <c r="N40" s="52"/>
-      <c r="O40" s="102"/>
-      <c r="P40" s="103"/>
-      <c r="Q40" s="57"/>
-      <c r="R40" s="97"/>
-      <c r="S40" s="98"/>
+      <c r="O40" s="80"/>
+      <c r="P40" s="81"/>
+      <c r="Q40" s="56"/>
+      <c r="R40" s="84"/>
+      <c r="S40" s="86"/>
     </row>
     <row r="41" spans="1:19" s="9" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A41" s="49"/>
@@ -4303,365 +4351,540 @@
       <c r="C41" s="78"/>
       <c r="D41" s="79"/>
       <c r="E41" s="51"/>
-      <c r="F41" s="86"/>
-      <c r="G41" s="87"/>
-      <c r="H41" s="87"/>
-      <c r="I41" s="87"/>
-      <c r="J41" s="87"/>
-      <c r="K41" s="87"/>
-      <c r="L41" s="104"/>
-      <c r="M41" s="105"/>
+      <c r="F41" s="147"/>
+      <c r="G41" s="148"/>
+      <c r="H41" s="148"/>
+      <c r="I41" s="148"/>
+      <c r="J41" s="148"/>
+      <c r="K41" s="148"/>
+      <c r="L41" s="96"/>
+      <c r="M41" s="97"/>
       <c r="N41" s="52"/>
-      <c r="O41" s="102"/>
-      <c r="P41" s="103"/>
+      <c r="O41" s="80"/>
+      <c r="P41" s="81"/>
       <c r="Q41" s="57"/>
-      <c r="R41" s="97"/>
-      <c r="S41" s="98"/>
+      <c r="R41" s="84"/>
+      <c r="S41" s="86"/>
     </row>
     <row r="42" spans="1:19" s="7" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="53"/>
       <c r="B42" s="54" t="s">
         <v>10</v>
       </c>
-      <c r="C42" s="203">
+      <c r="C42" s="107">
         <f>SUM(C30:D41)</f>
         <v>0</v>
       </c>
-      <c r="D42" s="233"/>
+      <c r="D42" s="108"/>
       <c r="E42" s="55"/>
-      <c r="F42" s="206"/>
-      <c r="G42" s="206"/>
-      <c r="H42" s="206"/>
-      <c r="I42" s="206"/>
-      <c r="J42" s="206"/>
-      <c r="K42" s="206"/>
-      <c r="L42" s="206"/>
-      <c r="M42" s="206"/>
-      <c r="N42" s="206"/>
-      <c r="O42" s="207" t="s">
+      <c r="F42" s="132"/>
+      <c r="G42" s="132"/>
+      <c r="H42" s="132"/>
+      <c r="I42" s="132"/>
+      <c r="J42" s="132"/>
+      <c r="K42" s="132"/>
+      <c r="L42" s="132"/>
+      <c r="M42" s="132"/>
+      <c r="N42" s="132"/>
+      <c r="O42" s="133" t="s">
         <v>42</v>
       </c>
-      <c r="P42" s="207"/>
-      <c r="Q42" s="208"/>
-      <c r="R42" s="203">
+      <c r="P42" s="133"/>
+      <c r="Q42" s="134"/>
+      <c r="R42" s="107">
         <f>SUM(R30:S41)</f>
         <v>0</v>
       </c>
-      <c r="S42" s="204"/>
+      <c r="S42" s="158"/>
     </row>
     <row r="43" spans="1:19" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="242" t="s">
+      <c r="A43" s="117" t="s">
         <v>57</v>
       </c>
-      <c r="B43" s="243"/>
-      <c r="C43" s="243"/>
-      <c r="D43" s="243"/>
-      <c r="E43" s="243"/>
-      <c r="F43" s="243"/>
-      <c r="G43" s="243"/>
-      <c r="H43" s="243"/>
-      <c r="I43" s="243"/>
-      <c r="J43" s="227"/>
-      <c r="K43" s="195" t="s">
+      <c r="B43" s="118"/>
+      <c r="C43" s="118"/>
+      <c r="D43" s="118"/>
+      <c r="E43" s="118"/>
+      <c r="F43" s="118"/>
+      <c r="G43" s="118"/>
+      <c r="H43" s="118"/>
+      <c r="I43" s="118"/>
+      <c r="J43" s="95"/>
+      <c r="K43" s="128" t="s">
         <v>58</v>
       </c>
-      <c r="L43" s="196"/>
-      <c r="M43" s="196"/>
-      <c r="N43" s="196"/>
-      <c r="O43" s="196"/>
-      <c r="P43" s="196"/>
-      <c r="Q43" s="216">
+      <c r="L43" s="129"/>
+      <c r="M43" s="129"/>
+      <c r="N43" s="129"/>
+      <c r="O43" s="129"/>
+      <c r="P43" s="129"/>
+      <c r="Q43" s="103">
         <f>SUM(Q26,R42)</f>
         <v>0</v>
       </c>
-      <c r="R43" s="216"/>
-      <c r="S43" s="217"/>
+      <c r="R43" s="103"/>
+      <c r="S43" s="104"/>
     </row>
     <row r="44" spans="1:19" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="228"/>
-      <c r="B44" s="229"/>
-      <c r="C44" s="229"/>
-      <c r="D44" s="229"/>
-      <c r="E44" s="229"/>
-      <c r="F44" s="229"/>
-      <c r="G44" s="229"/>
-      <c r="H44" s="229"/>
-      <c r="I44" s="229"/>
-      <c r="J44" s="230"/>
-      <c r="K44" s="210"/>
-      <c r="L44" s="211"/>
-      <c r="M44" s="211"/>
-      <c r="N44" s="211"/>
-      <c r="O44" s="211"/>
-      <c r="P44" s="211"/>
-      <c r="Q44" s="218"/>
-      <c r="R44" s="218"/>
-      <c r="S44" s="219"/>
+      <c r="A44" s="98"/>
+      <c r="B44" s="99"/>
+      <c r="C44" s="99"/>
+      <c r="D44" s="99"/>
+      <c r="E44" s="99"/>
+      <c r="F44" s="99"/>
+      <c r="G44" s="99"/>
+      <c r="H44" s="99"/>
+      <c r="I44" s="99"/>
+      <c r="J44" s="100"/>
+      <c r="K44" s="130"/>
+      <c r="L44" s="131"/>
+      <c r="M44" s="131"/>
+      <c r="N44" s="131"/>
+      <c r="O44" s="131"/>
+      <c r="P44" s="131"/>
+      <c r="Q44" s="105"/>
+      <c r="R44" s="105"/>
+      <c r="S44" s="106"/>
     </row>
     <row r="45" spans="1:19" ht="15" x14ac:dyDescent="0.2">
-      <c r="A45" s="225"/>
-      <c r="B45" s="226"/>
-      <c r="C45" s="226"/>
-      <c r="D45" s="226"/>
-      <c r="E45" s="226"/>
-      <c r="F45" s="226"/>
-      <c r="G45" s="226"/>
-      <c r="H45" s="226"/>
-      <c r="I45" s="226"/>
-      <c r="J45" s="227"/>
-      <c r="K45" s="195" t="s">
+      <c r="A45" s="93"/>
+      <c r="B45" s="94"/>
+      <c r="C45" s="94"/>
+      <c r="D45" s="94"/>
+      <c r="E45" s="94"/>
+      <c r="F45" s="94"/>
+      <c r="G45" s="94"/>
+      <c r="H45" s="94"/>
+      <c r="I45" s="94"/>
+      <c r="J45" s="95"/>
+      <c r="K45" s="128" t="s">
         <v>59</v>
       </c>
-      <c r="L45" s="196"/>
-      <c r="M45" s="196"/>
-      <c r="N45" s="196"/>
-      <c r="O45" s="196"/>
-      <c r="P45" s="196"/>
-      <c r="Q45" s="212">
+      <c r="L45" s="129"/>
+      <c r="M45" s="129"/>
+      <c r="N45" s="129"/>
+      <c r="O45" s="129"/>
+      <c r="P45" s="129"/>
+      <c r="Q45" s="139">
         <v>0</v>
       </c>
-      <c r="R45" s="212"/>
-      <c r="S45" s="213"/>
+      <c r="R45" s="139"/>
+      <c r="S45" s="140"/>
     </row>
     <row r="46" spans="1:19" ht="15" x14ac:dyDescent="0.2">
-      <c r="A46" s="225"/>
-      <c r="B46" s="226"/>
-      <c r="C46" s="226"/>
-      <c r="D46" s="226"/>
-      <c r="E46" s="226"/>
-      <c r="F46" s="226"/>
-      <c r="G46" s="226"/>
-      <c r="H46" s="226"/>
-      <c r="I46" s="226"/>
-      <c r="J46" s="227"/>
-      <c r="K46" s="210"/>
-      <c r="L46" s="211"/>
-      <c r="M46" s="211"/>
-      <c r="N46" s="211"/>
-      <c r="O46" s="211"/>
-      <c r="P46" s="211"/>
-      <c r="Q46" s="214"/>
-      <c r="R46" s="214"/>
-      <c r="S46" s="215"/>
+      <c r="A46" s="93"/>
+      <c r="B46" s="94"/>
+      <c r="C46" s="94"/>
+      <c r="D46" s="94"/>
+      <c r="E46" s="94"/>
+      <c r="F46" s="94"/>
+      <c r="G46" s="94"/>
+      <c r="H46" s="94"/>
+      <c r="I46" s="94"/>
+      <c r="J46" s="95"/>
+      <c r="K46" s="130"/>
+      <c r="L46" s="131"/>
+      <c r="M46" s="131"/>
+      <c r="N46" s="131"/>
+      <c r="O46" s="131"/>
+      <c r="P46" s="131"/>
+      <c r="Q46" s="141"/>
+      <c r="R46" s="141"/>
+      <c r="S46" s="142"/>
     </row>
     <row r="47" spans="1:19" ht="15" x14ac:dyDescent="0.2">
-      <c r="A47" s="225"/>
-      <c r="B47" s="226"/>
-      <c r="C47" s="226"/>
-      <c r="D47" s="226"/>
-      <c r="E47" s="226"/>
-      <c r="F47" s="226"/>
-      <c r="G47" s="226"/>
-      <c r="H47" s="226"/>
-      <c r="I47" s="226"/>
-      <c r="J47" s="227"/>
-      <c r="K47" s="195" t="s">
+      <c r="A47" s="93"/>
+      <c r="B47" s="94"/>
+      <c r="C47" s="94"/>
+      <c r="D47" s="94"/>
+      <c r="E47" s="94"/>
+      <c r="F47" s="94"/>
+      <c r="G47" s="94"/>
+      <c r="H47" s="94"/>
+      <c r="I47" s="94"/>
+      <c r="J47" s="95"/>
+      <c r="K47" s="128" t="s">
         <v>60</v>
       </c>
-      <c r="L47" s="196"/>
-      <c r="M47" s="196"/>
-      <c r="N47" s="196"/>
-      <c r="O47" s="196"/>
-      <c r="P47" s="196"/>
-      <c r="Q47" s="216">
+      <c r="L47" s="129"/>
+      <c r="M47" s="129"/>
+      <c r="N47" s="129"/>
+      <c r="O47" s="129"/>
+      <c r="P47" s="129"/>
+      <c r="Q47" s="103">
         <f>SUM(Q43-Q45)</f>
         <v>0</v>
       </c>
-      <c r="R47" s="216"/>
-      <c r="S47" s="217"/>
+      <c r="R47" s="103"/>
+      <c r="S47" s="104"/>
     </row>
     <row r="48" spans="1:19" ht="15" x14ac:dyDescent="0.2">
-      <c r="A48" s="225"/>
-      <c r="B48" s="226"/>
-      <c r="C48" s="226"/>
-      <c r="D48" s="226"/>
-      <c r="E48" s="226"/>
-      <c r="F48" s="226"/>
-      <c r="G48" s="226"/>
-      <c r="H48" s="226"/>
-      <c r="I48" s="226"/>
-      <c r="J48" s="227"/>
-      <c r="K48" s="210"/>
-      <c r="L48" s="211"/>
-      <c r="M48" s="211"/>
-      <c r="N48" s="211"/>
-      <c r="O48" s="211"/>
-      <c r="P48" s="211"/>
-      <c r="Q48" s="218"/>
-      <c r="R48" s="218"/>
-      <c r="S48" s="219"/>
+      <c r="A48" s="93"/>
+      <c r="B48" s="94"/>
+      <c r="C48" s="94"/>
+      <c r="D48" s="94"/>
+      <c r="E48" s="94"/>
+      <c r="F48" s="94"/>
+      <c r="G48" s="94"/>
+      <c r="H48" s="94"/>
+      <c r="I48" s="94"/>
+      <c r="J48" s="95"/>
+      <c r="K48" s="130"/>
+      <c r="L48" s="131"/>
+      <c r="M48" s="131"/>
+      <c r="N48" s="131"/>
+      <c r="O48" s="131"/>
+      <c r="P48" s="131"/>
+      <c r="Q48" s="105"/>
+      <c r="R48" s="105"/>
+      <c r="S48" s="106"/>
     </row>
     <row r="49" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="244"/>
-      <c r="B49" s="245"/>
-      <c r="C49" s="245"/>
-      <c r="D49" s="245"/>
-      <c r="E49" s="245"/>
-      <c r="F49" s="245"/>
-      <c r="G49" s="245"/>
-      <c r="H49" s="245"/>
-      <c r="I49" s="245"/>
-      <c r="J49" s="246"/>
-      <c r="K49" s="128" t="s">
+      <c r="A49" s="119"/>
+      <c r="B49" s="120"/>
+      <c r="C49" s="120"/>
+      <c r="D49" s="120"/>
+      <c r="E49" s="120"/>
+      <c r="F49" s="120"/>
+      <c r="G49" s="120"/>
+      <c r="H49" s="120"/>
+      <c r="I49" s="120"/>
+      <c r="J49" s="121"/>
+      <c r="K49" s="156" t="s">
         <v>61</v>
       </c>
-      <c r="L49" s="100"/>
-      <c r="M49" s="100"/>
-      <c r="N49" s="100"/>
+      <c r="L49" s="157"/>
+      <c r="M49" s="157"/>
+      <c r="N49" s="157"/>
       <c r="O49" s="47"/>
-      <c r="P49" s="209" t="s">
+      <c r="P49" s="137" t="s">
         <v>39</v>
       </c>
-      <c r="Q49" s="209"/>
+      <c r="Q49" s="137"/>
       <c r="R49" s="47"/>
       <c r="S49" s="48"/>
     </row>
     <row r="50" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A50" s="234" t="s">
+      <c r="A50" s="109" t="s">
         <v>12</v>
       </c>
-      <c r="B50" s="235"/>
-      <c r="C50" s="235"/>
-      <c r="D50" s="235"/>
-      <c r="E50" s="235"/>
-      <c r="F50" s="236"/>
-      <c r="G50" s="195" t="s">
+      <c r="B50" s="110"/>
+      <c r="C50" s="110"/>
+      <c r="D50" s="110"/>
+      <c r="E50" s="110"/>
+      <c r="F50" s="111"/>
+      <c r="G50" s="128" t="s">
         <v>62</v>
       </c>
-      <c r="H50" s="196"/>
-      <c r="I50" s="196"/>
-      <c r="J50" s="197"/>
-      <c r="K50" s="195" t="s">
+      <c r="H50" s="129"/>
+      <c r="I50" s="129"/>
+      <c r="J50" s="146"/>
+      <c r="K50" s="128" t="s">
         <v>63</v>
       </c>
-      <c r="L50" s="196"/>
-      <c r="M50" s="196"/>
-      <c r="N50" s="196"/>
-      <c r="O50" s="196"/>
-      <c r="P50" s="196"/>
-      <c r="Q50" s="198" t="s">
+      <c r="L50" s="129"/>
+      <c r="M50" s="129"/>
+      <c r="N50" s="129"/>
+      <c r="O50" s="129"/>
+      <c r="P50" s="129"/>
+      <c r="Q50" s="149" t="s">
         <v>11</v>
       </c>
-      <c r="R50" s="198"/>
-      <c r="S50" s="199"/>
+      <c r="R50" s="149"/>
+      <c r="S50" s="150"/>
     </row>
     <row r="51" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="237"/>
-      <c r="B51" s="238"/>
-      <c r="C51" s="238"/>
-      <c r="D51" s="238"/>
-      <c r="E51" s="238"/>
-      <c r="F51" s="239"/>
-      <c r="G51" s="194"/>
-      <c r="H51" s="193"/>
-      <c r="I51" s="193"/>
-      <c r="J51" s="205"/>
-      <c r="K51" s="192"/>
-      <c r="L51" s="193"/>
-      <c r="M51" s="193"/>
-      <c r="N51" s="193"/>
-      <c r="O51" s="193"/>
-      <c r="P51" s="193"/>
-      <c r="Q51" s="220"/>
-      <c r="R51" s="220"/>
-      <c r="S51" s="221"/>
+      <c r="A51" s="112"/>
+      <c r="B51" s="113"/>
+      <c r="C51" s="113"/>
+      <c r="D51" s="113"/>
+      <c r="E51" s="113"/>
+      <c r="F51" s="114"/>
+      <c r="G51" s="87"/>
+      <c r="H51" s="88"/>
+      <c r="I51" s="88"/>
+      <c r="J51" s="89"/>
+      <c r="K51" s="145"/>
+      <c r="L51" s="88"/>
+      <c r="M51" s="88"/>
+      <c r="N51" s="88"/>
+      <c r="O51" s="88"/>
+      <c r="P51" s="88"/>
+      <c r="Q51" s="82"/>
+      <c r="R51" s="82"/>
+      <c r="S51" s="83"/>
     </row>
     <row r="52" spans="1:19" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="240"/>
-      <c r="B52" s="241"/>
-      <c r="C52" s="241"/>
-      <c r="D52" s="241"/>
-      <c r="E52" s="241"/>
-      <c r="F52" s="230"/>
-      <c r="G52" s="194"/>
-      <c r="H52" s="193"/>
-      <c r="I52" s="193"/>
-      <c r="J52" s="205"/>
-      <c r="K52" s="194"/>
-      <c r="L52" s="193"/>
-      <c r="M52" s="193"/>
-      <c r="N52" s="193"/>
-      <c r="O52" s="193"/>
-      <c r="P52" s="193"/>
-      <c r="Q52" s="220"/>
-      <c r="R52" s="220"/>
-      <c r="S52" s="221"/>
+      <c r="A52" s="115"/>
+      <c r="B52" s="116"/>
+      <c r="C52" s="116"/>
+      <c r="D52" s="116"/>
+      <c r="E52" s="116"/>
+      <c r="F52" s="100"/>
+      <c r="G52" s="87"/>
+      <c r="H52" s="88"/>
+      <c r="I52" s="88"/>
+      <c r="J52" s="89"/>
+      <c r="K52" s="87"/>
+      <c r="L52" s="88"/>
+      <c r="M52" s="88"/>
+      <c r="N52" s="88"/>
+      <c r="O52" s="88"/>
+      <c r="P52" s="88"/>
+      <c r="Q52" s="82"/>
+      <c r="R52" s="82"/>
+      <c r="S52" s="83"/>
     </row>
     <row r="53" spans="1:19" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="234" t="s">
+      <c r="A53" s="109" t="s">
         <v>13</v>
       </c>
-      <c r="B53" s="235"/>
-      <c r="C53" s="235"/>
-      <c r="D53" s="235"/>
-      <c r="E53" s="235"/>
-      <c r="F53" s="236"/>
-      <c r="G53" s="195" t="s">
+      <c r="B53" s="110"/>
+      <c r="C53" s="110"/>
+      <c r="D53" s="110"/>
+      <c r="E53" s="110"/>
+      <c r="F53" s="111"/>
+      <c r="G53" s="128" t="s">
         <v>64</v>
       </c>
-      <c r="H53" s="196"/>
-      <c r="I53" s="196"/>
-      <c r="J53" s="197"/>
-      <c r="K53" s="190" t="s">
+      <c r="H53" s="129"/>
+      <c r="I53" s="129"/>
+      <c r="J53" s="146"/>
+      <c r="K53" s="143" t="s">
         <v>65</v>
       </c>
-      <c r="L53" s="191"/>
-      <c r="M53" s="191"/>
-      <c r="N53" s="191"/>
-      <c r="O53" s="191"/>
-      <c r="P53" s="191"/>
-      <c r="Q53" s="231" t="s">
+      <c r="L53" s="144"/>
+      <c r="M53" s="144"/>
+      <c r="N53" s="144"/>
+      <c r="O53" s="144"/>
+      <c r="P53" s="144"/>
+      <c r="Q53" s="101" t="s">
         <v>11</v>
       </c>
-      <c r="R53" s="231"/>
-      <c r="S53" s="232"/>
+      <c r="R53" s="101"/>
+      <c r="S53" s="102"/>
     </row>
     <row r="54" spans="1:19" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="237"/>
-      <c r="B54" s="238"/>
-      <c r="C54" s="238"/>
-      <c r="D54" s="238"/>
-      <c r="E54" s="238"/>
-      <c r="F54" s="239"/>
-      <c r="G54" s="194"/>
-      <c r="H54" s="193"/>
-      <c r="I54" s="193"/>
-      <c r="J54" s="205"/>
-      <c r="K54" s="247" t="s">
+      <c r="A54" s="112"/>
+      <c r="B54" s="113"/>
+      <c r="C54" s="113"/>
+      <c r="D54" s="113"/>
+      <c r="E54" s="113"/>
+      <c r="F54" s="114"/>
+      <c r="G54" s="87"/>
+      <c r="H54" s="88"/>
+      <c r="I54" s="88"/>
+      <c r="J54" s="89"/>
+      <c r="K54" s="122" t="s">
         <v>55</v>
       </c>
-      <c r="L54" s="248"/>
-      <c r="M54" s="248"/>
-      <c r="N54" s="248"/>
-      <c r="O54" s="248"/>
-      <c r="P54" s="248"/>
-      <c r="Q54" s="220"/>
-      <c r="R54" s="220"/>
-      <c r="S54" s="221"/>
+      <c r="L54" s="123"/>
+      <c r="M54" s="123"/>
+      <c r="N54" s="123"/>
+      <c r="O54" s="123"/>
+      <c r="P54" s="123"/>
+      <c r="Q54" s="82"/>
+      <c r="R54" s="82"/>
+      <c r="S54" s="83"/>
     </row>
     <row r="55" spans="1:19" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="240"/>
-      <c r="B55" s="241"/>
-      <c r="C55" s="241"/>
-      <c r="D55" s="241"/>
-      <c r="E55" s="241"/>
-      <c r="F55" s="230"/>
-      <c r="G55" s="222"/>
-      <c r="H55" s="223"/>
-      <c r="I55" s="223"/>
-      <c r="J55" s="224"/>
-      <c r="K55" s="249"/>
-      <c r="L55" s="250"/>
-      <c r="M55" s="250"/>
-      <c r="N55" s="250"/>
-      <c r="O55" s="250"/>
-      <c r="P55" s="250"/>
-      <c r="Q55" s="251"/>
-      <c r="R55" s="251"/>
-      <c r="S55" s="252"/>
+      <c r="A55" s="115"/>
+      <c r="B55" s="116"/>
+      <c r="C55" s="116"/>
+      <c r="D55" s="116"/>
+      <c r="E55" s="116"/>
+      <c r="F55" s="100"/>
+      <c r="G55" s="90"/>
+      <c r="H55" s="91"/>
+      <c r="I55" s="91"/>
+      <c r="J55" s="92"/>
+      <c r="K55" s="124"/>
+      <c r="L55" s="125"/>
+      <c r="M55" s="125"/>
+      <c r="N55" s="125"/>
+      <c r="O55" s="125"/>
+      <c r="P55" s="125"/>
+      <c r="Q55" s="126"/>
+      <c r="R55" s="126"/>
+      <c r="S55" s="127"/>
     </row>
   </sheetData>
   <mergeCells count="199">
+    <mergeCell ref="C39:D39"/>
+    <mergeCell ref="B28:B29"/>
+    <mergeCell ref="C28:D29"/>
+    <mergeCell ref="E28:E29"/>
+    <mergeCell ref="F30:K30"/>
+    <mergeCell ref="F28:K29"/>
+    <mergeCell ref="C40:D40"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="F32:K32"/>
+    <mergeCell ref="C34:D34"/>
+    <mergeCell ref="F34:K34"/>
+    <mergeCell ref="C38:D38"/>
+    <mergeCell ref="F38:K38"/>
+    <mergeCell ref="F33:K33"/>
+    <mergeCell ref="F35:K35"/>
+    <mergeCell ref="F40:K40"/>
+    <mergeCell ref="F39:K39"/>
+    <mergeCell ref="F37:K37"/>
+    <mergeCell ref="A28:A29"/>
+    <mergeCell ref="C37:D37"/>
+    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="C32:D32"/>
+    <mergeCell ref="C35:D35"/>
+    <mergeCell ref="O22:P22"/>
+    <mergeCell ref="E22:H22"/>
+    <mergeCell ref="E21:H21"/>
+    <mergeCell ref="E19:H19"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="O33:P33"/>
+    <mergeCell ref="O34:P34"/>
+    <mergeCell ref="L35:M35"/>
+    <mergeCell ref="F36:K36"/>
+    <mergeCell ref="O32:P32"/>
+    <mergeCell ref="L28:M29"/>
+    <mergeCell ref="O35:P35"/>
+    <mergeCell ref="O36:P36"/>
+    <mergeCell ref="N28:N29"/>
+    <mergeCell ref="O28:P29"/>
+    <mergeCell ref="O37:P37"/>
+    <mergeCell ref="L32:M32"/>
+    <mergeCell ref="L33:M33"/>
+    <mergeCell ref="L34:M34"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E20:H20"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="L26:M26"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="G26:H26"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="E25:H25"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="L24:M24"/>
+    <mergeCell ref="J17:N17"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="G5:K5"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="A4:S4"/>
+    <mergeCell ref="L5:S5"/>
+    <mergeCell ref="H1:S3"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="Q24:S24"/>
+    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="M8:N8"/>
+    <mergeCell ref="J20:K20"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="C16:F16"/>
+    <mergeCell ref="G6:K6"/>
+    <mergeCell ref="G7:K7"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="I9:K9"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="G8:K8"/>
+    <mergeCell ref="A8:F8"/>
+    <mergeCell ref="L6:S6"/>
+    <mergeCell ref="L7:S7"/>
+    <mergeCell ref="Q19:S19"/>
+    <mergeCell ref="M9:N9"/>
+    <mergeCell ref="A10:S10"/>
+    <mergeCell ref="O17:P17"/>
+    <mergeCell ref="L18:M18"/>
+    <mergeCell ref="L19:M19"/>
+    <mergeCell ref="P9:S9"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="E17:H17"/>
+    <mergeCell ref="K11:R11"/>
+    <mergeCell ref="Q17:S17"/>
+    <mergeCell ref="A15:F15"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="D11:H11"/>
+    <mergeCell ref="O19:P19"/>
+    <mergeCell ref="A13:F13"/>
+    <mergeCell ref="O18:P18"/>
+    <mergeCell ref="J19:K19"/>
+    <mergeCell ref="Q18:S18"/>
+    <mergeCell ref="A14:F14"/>
+    <mergeCell ref="E18:H18"/>
+    <mergeCell ref="G13:S13"/>
+    <mergeCell ref="N14:N15"/>
+    <mergeCell ref="Q20:S20"/>
+    <mergeCell ref="O20:P20"/>
+    <mergeCell ref="L20:M20"/>
+    <mergeCell ref="L22:M22"/>
+    <mergeCell ref="E24:H24"/>
+    <mergeCell ref="E23:H23"/>
+    <mergeCell ref="R39:S39"/>
+    <mergeCell ref="R40:S40"/>
+    <mergeCell ref="O40:P40"/>
+    <mergeCell ref="L40:M40"/>
+    <mergeCell ref="Q28:Q29"/>
+    <mergeCell ref="R28:S29"/>
+    <mergeCell ref="O25:P25"/>
+    <mergeCell ref="L25:M25"/>
+    <mergeCell ref="R27:S27"/>
+    <mergeCell ref="Q21:S21"/>
+    <mergeCell ref="Q22:S22"/>
+    <mergeCell ref="O39:P39"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="K53:P53"/>
+    <mergeCell ref="K51:P52"/>
+    <mergeCell ref="G53:J53"/>
+    <mergeCell ref="F31:K31"/>
+    <mergeCell ref="L31:M31"/>
+    <mergeCell ref="Q50:S50"/>
+    <mergeCell ref="Q26:S26"/>
+    <mergeCell ref="L21:M21"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="O23:P23"/>
+    <mergeCell ref="Q23:S23"/>
+    <mergeCell ref="O26:P26"/>
+    <mergeCell ref="K49:N49"/>
+    <mergeCell ref="R42:S42"/>
+    <mergeCell ref="L27:M27"/>
+    <mergeCell ref="F41:K41"/>
+    <mergeCell ref="R30:S30"/>
+    <mergeCell ref="L30:M30"/>
+    <mergeCell ref="G50:J50"/>
+    <mergeCell ref="G51:J52"/>
+    <mergeCell ref="L37:M37"/>
+    <mergeCell ref="R37:S37"/>
+    <mergeCell ref="K50:P50"/>
+    <mergeCell ref="O30:P30"/>
+    <mergeCell ref="R31:S31"/>
+    <mergeCell ref="F42:N42"/>
+    <mergeCell ref="O42:Q42"/>
+    <mergeCell ref="O31:P31"/>
+    <mergeCell ref="R41:S41"/>
+    <mergeCell ref="O21:P21"/>
+    <mergeCell ref="O27:P27"/>
+    <mergeCell ref="R32:S32"/>
+    <mergeCell ref="R33:S33"/>
+    <mergeCell ref="R34:S34"/>
+    <mergeCell ref="P49:Q49"/>
+    <mergeCell ref="F27:K27"/>
+    <mergeCell ref="K47:P48"/>
+    <mergeCell ref="Q45:S46"/>
+    <mergeCell ref="Q47:S48"/>
+    <mergeCell ref="L39:M39"/>
+    <mergeCell ref="R35:S35"/>
+    <mergeCell ref="O38:P38"/>
+    <mergeCell ref="L38:M38"/>
+    <mergeCell ref="R38:S38"/>
+    <mergeCell ref="R36:S36"/>
+    <mergeCell ref="L36:M36"/>
     <mergeCell ref="C41:D41"/>
     <mergeCell ref="O41:P41"/>
     <mergeCell ref="Q51:S52"/>
@@ -4686,185 +4909,10 @@
     <mergeCell ref="Q54:S55"/>
     <mergeCell ref="K43:P44"/>
     <mergeCell ref="K45:P46"/>
-    <mergeCell ref="K50:P50"/>
-    <mergeCell ref="O39:P39"/>
-    <mergeCell ref="R40:S40"/>
-    <mergeCell ref="F42:N42"/>
-    <mergeCell ref="O42:Q42"/>
-    <mergeCell ref="O40:P40"/>
-    <mergeCell ref="R41:S41"/>
-    <mergeCell ref="O21:P21"/>
-    <mergeCell ref="O27:P27"/>
-    <mergeCell ref="R30:S30"/>
-    <mergeCell ref="R31:S31"/>
-    <mergeCell ref="R32:S32"/>
-    <mergeCell ref="P49:Q49"/>
-    <mergeCell ref="F27:K27"/>
-    <mergeCell ref="K47:P48"/>
-    <mergeCell ref="Q45:S46"/>
-    <mergeCell ref="Q47:S48"/>
-    <mergeCell ref="L37:M37"/>
-    <mergeCell ref="R33:S33"/>
-    <mergeCell ref="O36:P36"/>
-    <mergeCell ref="L36:M36"/>
-    <mergeCell ref="R36:S36"/>
-    <mergeCell ref="R34:S34"/>
-    <mergeCell ref="L34:M34"/>
-    <mergeCell ref="C40:D40"/>
-    <mergeCell ref="K53:P53"/>
-    <mergeCell ref="K51:P52"/>
-    <mergeCell ref="G53:J53"/>
-    <mergeCell ref="F40:K40"/>
-    <mergeCell ref="L40:M40"/>
-    <mergeCell ref="Q50:S50"/>
-    <mergeCell ref="Q26:S26"/>
-    <mergeCell ref="L21:M21"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="O23:P23"/>
-    <mergeCell ref="Q23:S23"/>
-    <mergeCell ref="O26:P26"/>
-    <mergeCell ref="K49:N49"/>
-    <mergeCell ref="R42:S42"/>
-    <mergeCell ref="L27:M27"/>
-    <mergeCell ref="F41:K41"/>
-    <mergeCell ref="R39:S39"/>
-    <mergeCell ref="L39:M39"/>
-    <mergeCell ref="G50:J50"/>
-    <mergeCell ref="G51:J52"/>
-    <mergeCell ref="L35:M35"/>
-    <mergeCell ref="R35:S35"/>
-    <mergeCell ref="Q20:S20"/>
-    <mergeCell ref="O20:P20"/>
-    <mergeCell ref="L20:M20"/>
-    <mergeCell ref="L22:M22"/>
-    <mergeCell ref="E24:H24"/>
-    <mergeCell ref="E23:H23"/>
-    <mergeCell ref="R37:S37"/>
-    <mergeCell ref="R38:S38"/>
-    <mergeCell ref="O38:P38"/>
-    <mergeCell ref="L38:M38"/>
-    <mergeCell ref="Q28:Q29"/>
-    <mergeCell ref="R28:S29"/>
-    <mergeCell ref="O25:P25"/>
-    <mergeCell ref="L25:M25"/>
-    <mergeCell ref="R27:S27"/>
-    <mergeCell ref="Q21:S21"/>
-    <mergeCell ref="Q22:S22"/>
-    <mergeCell ref="O37:P37"/>
-    <mergeCell ref="M9:N9"/>
-    <mergeCell ref="A10:S10"/>
-    <mergeCell ref="O17:P17"/>
-    <mergeCell ref="L18:M18"/>
-    <mergeCell ref="L19:M19"/>
-    <mergeCell ref="P9:S9"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="E17:H17"/>
-    <mergeCell ref="K11:R11"/>
-    <mergeCell ref="Q17:S17"/>
-    <mergeCell ref="A15:F15"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="D11:H11"/>
-    <mergeCell ref="O19:P19"/>
-    <mergeCell ref="A13:F13"/>
-    <mergeCell ref="O18:P18"/>
-    <mergeCell ref="J19:K19"/>
-    <mergeCell ref="Q18:S18"/>
-    <mergeCell ref="A14:F14"/>
-    <mergeCell ref="E18:H18"/>
-    <mergeCell ref="G13:S13"/>
-    <mergeCell ref="N14:N15"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="G5:K5"/>
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="A4:S4"/>
-    <mergeCell ref="L5:S5"/>
-    <mergeCell ref="H1:S3"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="Q24:S24"/>
-    <mergeCell ref="A7:F7"/>
-    <mergeCell ref="M8:N8"/>
-    <mergeCell ref="J20:K20"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="C16:F16"/>
-    <mergeCell ref="G6:K6"/>
-    <mergeCell ref="G7:K7"/>
-    <mergeCell ref="D9:E9"/>
-    <mergeCell ref="I9:K9"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="G8:K8"/>
-    <mergeCell ref="A8:F8"/>
-    <mergeCell ref="L6:S6"/>
-    <mergeCell ref="L7:S7"/>
-    <mergeCell ref="Q19:S19"/>
-    <mergeCell ref="A27:D27"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="E20:H20"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="L26:M26"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="G26:H26"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="E25:H25"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="L24:M24"/>
-    <mergeCell ref="J17:N17"/>
-    <mergeCell ref="A28:A29"/>
-    <mergeCell ref="C35:D35"/>
-    <mergeCell ref="C34:D34"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="C33:D33"/>
-    <mergeCell ref="O22:P22"/>
-    <mergeCell ref="E22:H22"/>
-    <mergeCell ref="E21:H21"/>
-    <mergeCell ref="E19:H19"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="O31:P31"/>
-    <mergeCell ref="O32:P32"/>
-    <mergeCell ref="L33:M33"/>
-    <mergeCell ref="F34:K34"/>
-    <mergeCell ref="O30:P30"/>
-    <mergeCell ref="L28:M29"/>
-    <mergeCell ref="O33:P33"/>
-    <mergeCell ref="O34:P34"/>
-    <mergeCell ref="N28:N29"/>
-    <mergeCell ref="O28:P29"/>
-    <mergeCell ref="O35:P35"/>
-    <mergeCell ref="L30:M30"/>
-    <mergeCell ref="L31:M31"/>
-    <mergeCell ref="L32:M32"/>
-    <mergeCell ref="C37:D37"/>
-    <mergeCell ref="B28:B29"/>
-    <mergeCell ref="C28:D29"/>
-    <mergeCell ref="E28:E29"/>
-    <mergeCell ref="F39:K39"/>
-    <mergeCell ref="F28:K29"/>
-    <mergeCell ref="C38:D38"/>
-    <mergeCell ref="C39:D39"/>
-    <mergeCell ref="C31:D31"/>
-    <mergeCell ref="F30:K30"/>
-    <mergeCell ref="C32:D32"/>
-    <mergeCell ref="F32:K32"/>
-    <mergeCell ref="C36:D36"/>
-    <mergeCell ref="F36:K36"/>
-    <mergeCell ref="F31:K31"/>
-    <mergeCell ref="F33:K33"/>
-    <mergeCell ref="F38:K38"/>
-    <mergeCell ref="F37:K37"/>
-    <mergeCell ref="F35:K35"/>
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0" footer="0.5"/>
-  <pageSetup scale="80" orientation="portrait" r:id="rId1"/>
+  <pageSetup scale="82" orientation="portrait" r:id="rId1"/>
   <headerFooter alignWithMargins="0"/>
   <drawing r:id="rId2"/>
   <legacyDrawing r:id="rId3"/>
@@ -5022,7 +5070,7 @@
         <v>13</v>
       </c>
       <c r="B18" s="253" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C18" s="253"/>
     </row>
@@ -5085,7 +5133,7 @@
         <v>20</v>
       </c>
       <c r="B25" s="253" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C25" s="253"/>
     </row>
@@ -5103,7 +5151,7 @@
         <v>22</v>
       </c>
       <c r="B27" s="253" t="s">
-        <v>98</v>
+        <v>109</v>
       </c>
       <c r="C27" s="253"/>
     </row>
@@ -5112,7 +5160,7 @@
         <v>23</v>
       </c>
       <c r="B28" s="253" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C28" s="253"/>
     </row>
@@ -5130,7 +5178,7 @@
         <v>25</v>
       </c>
       <c r="B30" s="253" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C30" s="253"/>
     </row>
@@ -5148,7 +5196,7 @@
         <v>27</v>
       </c>
       <c r="B32" s="253" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C32" s="253"/>
     </row>
@@ -5166,7 +5214,7 @@
         <v>29</v>
       </c>
       <c r="B34" s="253" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C34" s="253"/>
     </row>
@@ -5175,7 +5223,7 @@
         <v>30</v>
       </c>
       <c r="B35" s="253" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C35" s="253"/>
     </row>
@@ -5184,7 +5232,7 @@
         <v>31</v>
       </c>
       <c r="B36" s="253" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C36" s="253"/>
     </row>
@@ -5193,7 +5241,7 @@
         <v>32</v>
       </c>
       <c r="B37" s="253" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C37" s="253"/>
     </row>
@@ -5202,13 +5250,37 @@
         <v>33</v>
       </c>
       <c r="B38" s="253" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C38" s="253"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="OkP2orKJ6xHvNwGKNs068EcyiReU/QOZPgkR62amMkhk7mA6wZTUeyZjloxOHrfUzhM2MH7VgUcQzcPhyEO6EA==" saltValue="DsVQ+306ImdFYoVI5uX3kA==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="3rwC03f1uGZc2ztGW5geghtnykiMBNAMQvuuQt3XcQpIwpTlVRr5tpylAa9/AtKT4IcG+m2iEysX9fK96jbnWQ==" saltValue="oVyxomNWFD8+NEr5ZML52g==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="36">
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="B25:C25"/>
     <mergeCell ref="B14:C14"/>
     <mergeCell ref="B1:C1"/>
     <mergeCell ref="B2:C2"/>
@@ -5221,30 +5293,6 @@
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B12:C12"/>
     <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B37:C37"/>
   </mergeCells>
   <pageMargins left="0.17" right="0.17" top="0.75" bottom="0.43" header="0.3" footer="0.3"/>
   <pageSetup scale="98" orientation="portrait" r:id="rId1"/>
@@ -5257,18 +5305,27 @@
     <PublishingExpirationDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
     <PublishingStartDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
     <Document_x0020_title xmlns="9333e0c0-1495-4f6e-9f18-9c5629cbe005">
-      <Url>https://www.oregon.gov/das/Financial/Acctng/Documents/75.40.01.FO.xlsx</Url>
+      <Url>https://www-auth.oregon.gov/das/Financial/Acctng/Documents/75.40.01.FO.xlsx</Url>
       <Description>Travel Expense Detail Sheet</Description>
     </Document_x0020_title>
     <Chapter xmlns="9333e0c0-1495-4f6e-9f18-9c5629cbe005">75 - Forms</Chapter>
     <Alpha_x002f_Number xmlns="9333e0c0-1495-4f6e-9f18-9c5629cbe005">75.40.01.fo</Alpha_x002f_Number>
-    <Effective_x0020_Date xmlns="9333e0c0-1495-4f6e-9f18-9c5629cbe005">January 1, 2026</Effective_x0020_Date>
+    <Effective_x0020_Date xmlns="9333e0c0-1495-4f6e-9f18-9c5629cbe005">07/01/2026</Effective_x0020_Date>
     <Topic_x0020_Area xmlns="9333e0c0-1495-4f6e-9f18-9c5629cbe005">OAM</Topic_x0020_Area>
   </documentManagement>
 </p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100CE0E7A523623CB4F8C0C3CD503D8FBAF" ma:contentTypeVersion="22" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="2f88af8ebe6c0e5e4080537d02f2354d">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="9333e0c0-1495-4f6e-9f18-9c5629cbe005" xmlns:ns3="c11a4dd1-9999-41de-ad6b-508521c3559d" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="526374552003716673657cf7ac973ec1" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -5509,15 +5566,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{634087B9-89AA-4804-B2F9-C534E2986D74}">
   <ds:schemaRefs>
@@ -5530,10 +5578,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E4081034-CED8-4274-BB00-2DF25EC7D8F0}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4A928F4D-BB76-4859-8376-6A85BEB0AD2B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
@@ -5541,6 +5585,10 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E7235E30-FC71-4982-AE5E-9672022CE203}"/>
+</file>
+
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{09b73270-2993-4076-be47-9c78f42a1e84}" enabled="1" method="Privileged" siteId="{aa3f6932-fa7c-47b4-a0ce-a598cad161cf}" contentBits="0" removed="0"/>
